--- a/docs/xlsx/jobs-2026-10-13.xlsx
+++ b/docs/xlsx/jobs-2026-10-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="598">
   <si>
     <t>Title</t>
   </si>
@@ -94,6 +94,48 @@
     <t>https://www.conservationjobboard.com/job-listing-campus-organizer-berkeley-california/6496251803</t>
   </si>
   <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campus-organizer-los-angeles-california/3051412299</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campus-organizer-austin-texas/9429279633</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campus-organizer-boston-massachusetts/2519037362</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campus-organizer-philadelphia-pennsylvania/3196915177</t>
+  </si>
+  <si>
+    <t>Community Outreach Specialist</t>
+  </si>
+  <si>
+    <t>Prior Lake-Spring Lake Watershed District</t>
+  </si>
+  <si>
+    <t>Prior Lake, MN</t>
+  </si>
+  <si>
+    <t>$59,000 - $68,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-outreach-specialist-prior-lake-minnesota/7574472850</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
@@ -112,6 +154,48 @@
     <t>https://www.conservationjobboard.com/job-listing-development-manager-corvallis-oregon/2529628249</t>
   </si>
   <si>
+    <t>Environmental Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>For positions starting in August 2027, the target annual compensation is $41,000 (but compensation may range between $41,000 and $44,450 depending on location).</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaign-organizer-portland-oregon/9024325155</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaign-organizer-chicago-illinois/6312126239</t>
+  </si>
+  <si>
+    <t>Environmental Education Internship</t>
+  </si>
+  <si>
+    <t>Fossil Rim Wildlife Center</t>
+  </si>
+  <si>
+    <t>Glen Rose, TX</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$400 per month</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-internship-glen-rose-texas/5352695845</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -130,6 +214,72 @@
     <t>https://www.conservationjobboard.com/job-listing-executive-director-gulf-shores-alabama/9417165425</t>
   </si>
   <si>
+    <t>Human Resource Assistant Director</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Topeka, KS</t>
+  </si>
+  <si>
+    <t>$27.25 - $30.25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-human-resource-assistant-director-topeka-kansas/5277149813</t>
+  </si>
+  <si>
+    <t>Marine Conservation Internship (Spring 2027)</t>
+  </si>
+  <si>
+    <t>Loggerhead Marinelife Center</t>
+  </si>
+  <si>
+    <t>Juno Beach, FL</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-conservation-internship-spring-2027-juno-beach-florida/3402964444</t>
+  </si>
+  <si>
+    <t>Marine Education Internship(Spring 2027)</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-education-internshipspring-2027-juno-beach-florida/6148717937</t>
+  </si>
+  <si>
+    <t>MS and PhD Students in Environmental Governance</t>
+  </si>
+  <si>
+    <t>Colorado State University</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$2,300 - $2,500 per month</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ms-and-phd-students-in-environmental-governance-fort-collins-colorado/9504365639</t>
+  </si>
+  <si>
     <t>Outdoor Trip Leader</t>
   </si>
   <si>
@@ -139,9 +289,6 @@
     <t>Brunswick, ME</t>
   </si>
   <si>
-    <t>Temporary</t>
-  </si>
-  <si>
     <t>$2,500 - $3,000 per month</t>
   </si>
   <si>
@@ -151,6 +298,54 @@
     <t>https://www.conservationjobboard.com/job-listing-outdoor-trip-leader-brunswick-maine/2805376719</t>
   </si>
   <si>
+    <t>Postdoctoral Research Associate - Wildlife Genetics</t>
+  </si>
+  <si>
+    <t>Illinois Natural History Survey at the University of Illinois Urbana-Champaign</t>
+  </si>
+  <si>
+    <t>Champaign, IL</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$60,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-research-associate---wildlife-genetics-champaign-illinois/3469640398</t>
+  </si>
+  <si>
+    <t>Public Lands Manager I</t>
+  </si>
+  <si>
+    <t>Great Bend, KS</t>
+  </si>
+  <si>
+    <t>$25.73 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-manager-i-great-bend-kansas/6597563577</t>
+  </si>
+  <si>
+    <t>Public Lands Manager II</t>
+  </si>
+  <si>
+    <t>Parsons, KS</t>
+  </si>
+  <si>
+    <t>$28.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-manager-ii-parsons-kansas/9926993583</t>
+  </si>
+  <si>
     <t>Regional Director - REMOTE</t>
   </si>
   <si>
@@ -169,25 +364,1450 @@
     <t>https://www.conservationjobboard.com/job-listing-regional-director---remote-lansing-michigan/8836700306</t>
   </si>
   <si>
+    <t>Research Scientist, Ecology</t>
+  </si>
+  <si>
+    <t>Atlanta Botanical Garden</t>
+  </si>
+  <si>
+    <t>Atlanta, GA</t>
+  </si>
+  <si>
+    <t>salary commensurate with experience</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-scientist-ecology-atlanta-georgia/2124778726</t>
+  </si>
+  <si>
+    <t>School Year Program Instructor (2026–2027)</t>
+  </si>
+  <si>
+    <t>Vida Verde Nature Education</t>
+  </si>
+  <si>
+    <t>San Gregorio, CA</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-school-year-program-instructor-20262027-san-gregorio-california/6708616720</t>
+  </si>
+  <si>
+    <t>Site and Research Manager ; Goualougo (Nouabalé-Ndoki ,Republic of Congo)</t>
+  </si>
+  <si>
+    <t>Wild Conservation Society</t>
+  </si>
+  <si>
+    <t>Goualougo, Africa</t>
+  </si>
+  <si>
+    <t>Competitive Salary commensurate with Experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-site-and-research-manager--goualougo-nouabal-ndoki-republic-of-congo-goualougo-africa/3655232356</t>
+  </si>
+  <si>
+    <t>Site and Research Manager ; Mondika (Nouabalé-Ndoki National Park), Republic of congo.</t>
+  </si>
+  <si>
+    <t>Mondika, Africa</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-site-and-research-manager--mondika-nouabal-ndoki-national-park-republic-of-congo-mondika-africa/9537005430</t>
+  </si>
+  <si>
+    <t>TPWD - Administrative Assistant V (Office Manager)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>Del Rio, TX</t>
+  </si>
+  <si>
+    <t>$4,769.07 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---administrative-assistant-v-office-manager-del-rio-texas/9955273261</t>
+  </si>
+  <si>
+    <t>TWDB - 27-08 Flood Management Evaluation Engineer/Project Manager (Engineer II - V/Project Manager II - IV)</t>
+  </si>
+  <si>
+    <t>Texas Water Development Board</t>
+  </si>
+  <si>
+    <t>$6,100 - $8,610 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---27-08-flood-management-evaluation-engineerproject-manager-engineer-ii---vproject-manager-ii---iv-austin-texas/8703858206</t>
+  </si>
+  <si>
+    <t>Weekend Building Supervisor</t>
+  </si>
+  <si>
+    <t>The Watershed Institute</t>
+  </si>
+  <si>
+    <t>Pennington, NJ</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-weekend-building-supervisor-pennington-new-jersey/1613708231</t>
+  </si>
+  <si>
+    <t>Wildlife Biologist - Nuisance Wildlife</t>
+  </si>
+  <si>
+    <t>Wildernex LLC Wildlife Control</t>
+  </si>
+  <si>
+    <t>Dallas, TX</t>
+  </si>
+  <si>
+    <t>$45,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist---nuisance-wildlife-dallas-texas/6516294347</t>
+  </si>
+  <si>
+    <t>Sarasota, FL</t>
+  </si>
+  <si>
+    <t>$45,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist---nuisance-wildlife-sarasota-florida/2642511521</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation &amp; Management Internship</t>
+  </si>
+  <si>
+    <t>Florida Fish &amp; Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-conservation--management-internship-tallahassee-florida/6832817656</t>
+  </si>
+  <si>
+    <t>Wildlife Management Temporary (16 positions)</t>
+  </si>
+  <si>
+    <t>Iowa Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Multiple, IA</t>
+  </si>
+  <si>
+    <t>$15.25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-management-temporary-16-positions-multiple-iowa/4118616062</t>
+  </si>
+  <si>
+    <t>Illinois Valley Watershed Council</t>
+  </si>
+  <si>
+    <t>Cave Junction, Oregon, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>60,000 - 80,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/executive-director-212/</t>
+  </si>
+  <si>
+    <t>Regional Program Manager, School Indoor Air Quality Program (Southwest)</t>
+  </si>
+  <si>
+    <t>U.S. Green Building Council</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Green Building</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/regional-program-manager-school-indoor-air-quality-program-southwest/</t>
+  </si>
+  <si>
+    <t>SARE Grant Program Admin – Partnership Grant</t>
+  </si>
+  <si>
+    <t>University of Vermont</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont, United States</t>
+  </si>
+  <si>
+    <t>40,000 - 60,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/sare-grant-program-admin-partnership-grant/</t>
+  </si>
+  <si>
+    <t>Senior Specialist, Building Science &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Institute for Market Transformation</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Sustainability</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-specialist-building-science-analysis/</t>
+  </si>
+  <si>
+    <t>Advocacy Specialist: Treaty Bodies</t>
+  </si>
+  <si>
+    <t>ILGA World - The International Lesbian Gay Bisexual Trans and Intersex Association</t>
+  </si>
+  <si>
+    <t>Geneva, Geneva, CH</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>CHF 81060.00 - 81060.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a04bf96ff9ee4dffbcc2397a6492e895-advocacy-specialist-treaty-bodies-ilga-world-the-international-lesbian-gay-bisexual-trans-and-intersex-association-geneva</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>LIFE UNLIMITED INC</t>
+  </si>
+  <si>
+    <t>North Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 260000.00 - 260000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2930639dc2a64ae8900204cfa2a78442-chief-executive-officer-life-unlimited-inc-north-kansas-city</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>HomeFront (Mercer County, NJ)</t>
+  </si>
+  <si>
+    <t>Lawrence Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33ab1d9138b14e27a2512492f66d3c9c-chief-financial-officer-homefront-mercer-county-nj-lawrence-township</t>
+  </si>
+  <si>
+    <t>Client Assistant</t>
+  </si>
+  <si>
+    <t>Doorways</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6df587467c5437588ffb86313362176-client-assistant-doorways-arlington</t>
+  </si>
+  <si>
+    <t>Client Care Coordinator (LMSW)</t>
+  </si>
+  <si>
+    <t>Siena House Shelter</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fb67c278e7c494e8664b1a85695cebd-client-care-coordinator-lmsw-siena-house-shelter-bronx</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Onja</t>
+  </si>
+  <si>
+    <t>Toamasina, Atsinanana, MG</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1b687d1e74242e29b4d99b08f220b09-communications-manager-onja-toamasina</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>PACT- People Acting in Community Together</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6fc331e8fa0403c81ef351a0e1c3253-community-organizer-pact-people-acting-in-community-together-san-jose</t>
+  </si>
+  <si>
+    <t>Community Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Animal Welfare League of Arlington</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab795244c5a4452ca94e1bbcd18789ab-community-outreach-coordinator-animal-welfare-league-of-arlington-arlington</t>
+  </si>
+  <si>
+    <t>Community Programs Officer</t>
+  </si>
+  <si>
+    <t>Community Foundation Santa Cruz County</t>
+  </si>
+  <si>
+    <t>Aptos, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08d152f20df144c997585b64ef253fcc-community-programs-officer-community-foundation-santa-cruz-county-aptos</t>
+  </si>
+  <si>
+    <t>Coordinador/a de Desarrollo de Fondos y Alianzas</t>
+  </si>
+  <si>
+    <t>ASDRA Asociación Síndrome de Down de la República Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, C, AR</t>
+  </si>
+  <si>
+    <t>Disability, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04c9c56727f54adc8e6e6c3c3f00ff58-coordinadora-de-desarrollo-de-fondos-y-alianzas-asdra-asociacion-sindrome-de-down-de-la-republica-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Counsellor</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a21dee8b8a8345a68af1176de662a6b0-counsellor-onja-toamasina</t>
+  </si>
+  <si>
+    <t>Creative Director</t>
+  </si>
+  <si>
+    <t>Education Reimagined</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3c80337ee154c2985379872619d624d-creative-director-education-reimagined-washington</t>
+  </si>
+  <si>
+    <t>Dance Instructor (Prospect Park YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45343985ea884b5e9d63958c08b4e083-dance-instructor-prospect-park-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>David and Francie Horvitz Family Foundation Director-The Gund at Kenyon College working with Management Consultants for the Arts</t>
+  </si>
+  <si>
+    <t>Management Consultants for the Arts, Inc.</t>
+  </si>
+  <si>
+    <t>Gambier, Ohio</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/accdffea97f944a5b2373e4ae97321b0-david-and-francie-horvitz-family-foundation-director-the-gund-at-kenyon-college-working-with-management-consultants-for-the-arts-management-consultants-for-the-arts-inc-gambier</t>
+  </si>
+  <si>
+    <t>Day Camp Director</t>
+  </si>
+  <si>
+    <t>Trail Blazers</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9aca6b09c8a941b59ce05aef2ffb5f06-day-camp-director-trail-blazers-kings-county</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Translate Gender</t>
+  </si>
+  <si>
+    <t>Northampton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c7d25b8e1924ccdb97370dd9277b20c-development-director-translate-gender-northampton</t>
+  </si>
+  <si>
+    <t>Renaissance Youth Center</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce52b0ce707e44d894048cb073745f92-development-director-renaissance-youth-center-bronx-county</t>
+  </si>
+  <si>
+    <t>Development Officer, West Coast</t>
+  </si>
+  <si>
+    <t>Build Health International</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Water Sanitation, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c91335ad14d460d8765fd260a7226d2-development-officer-west-coast-build-health-international-san-francisco</t>
+  </si>
+  <si>
+    <t>Director - New York</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56d32d5dd33f41edaa3f338c80c01372-director-new-york-the-posse-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>NC Coalition for Alternatives to the Death Penalty</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Crime Safety, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09c2fada6a9b406a96b082bcb3f2ad6e-director-of-communications-nc-coalition-for-alternatives-to-the-death-penalty-durham</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Disability Rights Advocates</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cf48fc5852c4dbcabafed2d42bfde74-director-of-development-disability-rights-advocates-new-york</t>
+  </si>
+  <si>
+    <t>Park City Conservation Association dba Recycle Utah</t>
+  </si>
+  <si>
+    <t>Park City, UT</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/974dcc1fabd14bee8168debd81b7ad7a-director-of-development-park-city-conservation-association-dba-recycle-utah-park-city</t>
+  </si>
+  <si>
+    <t>Director of Resource Development</t>
+  </si>
+  <si>
+    <t>The Neighborhood Developers</t>
+  </si>
+  <si>
+    <t>Chelsea, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ffa3fdc331d4b0c9f7f2c0fff20e782-director-of-resource-development-the-neighborhood-developers-chelsea</t>
+  </si>
+  <si>
+    <t>Director of Social Services (LCSW)</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cba17aa288244d794da3453673d7b33-director-of-social-services-lcsw-siena-house-shelter-bronx</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>American Federation of Musicians and Employers Pension Fund</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58bf11bc12ea40308ed3dcbe443f847c-education-coordinator-american-federation-of-musicians-and-employers-pension-fund-new-york</t>
+  </si>
+  <si>
+    <t>Employment Attorney/Of Counsel</t>
+  </si>
+  <si>
+    <t>Harmon Curran Spielberg &amp; Eisenberg, LLP</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/81a7e89938f84999ae10adca3a91ba78-employment-attorneyof-counsel-harmon-curran-spielberg-eisenberg-llp-washington</t>
+  </si>
+  <si>
+    <t>End of Year Campaign Manager</t>
+  </si>
+  <si>
+    <t>Elba Hope Foundation</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 4500.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdeba5d720ed4ea48af336fd1da88297-end-of-year-campaign-manager-elba-hope-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Enrollment Operations Manager</t>
+  </si>
+  <si>
+    <t>School Year Abroad</t>
+  </si>
+  <si>
+    <t>North Andover, Massachusetts</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/601955b9ce074ea4bedda28157ce2561-enrollment-operations-manager-school-year-abroad-north-andover</t>
+  </si>
+  <si>
+    <t>Evaluation Associate</t>
+  </si>
+  <si>
+    <t>The Episcopal Health Foundation</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>USD 83200.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf45c6f7a6e04d35aeb00ffa58e2aaf7-evaluation-associate-the-episcopal-health-foundation-houston</t>
+  </si>
+  <si>
+    <t>Everytown Labs Fellow</t>
+  </si>
+  <si>
+    <t>Everytown For Gun Safety</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fc2604079004598852f8983cec72abf-everytown-labs-fellow-everytown-for-gun-safety-new-york</t>
+  </si>
+  <si>
+    <t>Executive Administrative Partner</t>
+  </si>
+  <si>
+    <t>Agog</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>USD 93600.00 - 114004.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Science Technology, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7f9e98a26c284e4692be3d5f99a0c390-executive-administrative-partner-agog-los-angeles</t>
+  </si>
+  <si>
+    <t>Family Services Coordinator</t>
+  </si>
+  <si>
+    <t>ECDO</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c722217d1ba747db951d6ed015400317-family-services-coordinator-ecdo-new-york</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Appalachian Mountain Club</t>
+  </si>
+  <si>
+    <t>Gorham, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 68685.00 - 87058.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34f49b825d3c44e8b55dc99800360fc7-finance-manager-appalachian-mountain-club-gorham</t>
+  </si>
+  <si>
+    <t>Fitness Center Coach (Park Slope Armory YMCA)</t>
+  </si>
+  <si>
+    <t>USD 17.17 - 17.17/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4e706495c7a40e7bba9d2e78d5b539c-fitness-center-coach-park-slope-armory-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Grant Accountant</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80fdd3b8b876450fa98c41b692801ea0-grant-accountant-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Growth Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7108ad7d6b234bb5b943685c5d060b15-growth-manager-onja-toamasina</t>
+  </si>
+  <si>
+    <t>Healthcare Associate</t>
+  </si>
+  <si>
+    <t>Isaacson, Miller</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d52edec8d6024259abf5c319b1100f45-healthcare-associate-isaacson-miller-boston</t>
+  </si>
+  <si>
+    <t>Immigration Attorney</t>
+  </si>
+  <si>
+    <t>Research Foundation of CUNY</t>
+  </si>
+  <si>
+    <t>USD 104584.00 - 113299.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c3aed6b718364ad68387cc461ae956dd-immigration-attorney-research-foundation-of-cuny-new-york</t>
+  </si>
+  <si>
+    <t>Individual Giving Manager</t>
+  </si>
+  <si>
+    <t>New York Focus</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Media, Policy, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fc70aa2e6894742be75ab3f94d21140-individual-giving-manager-new-york-focus-new-york</t>
+  </si>
+  <si>
+    <t>Individual Giving Manager (On-Site)</t>
+  </si>
+  <si>
+    <t>Young People's Chorus of NYC</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed6bfb0782f44d8396fddb65e934861d-individual-giving-manager-on-site-young-peoples-chorus-of-nyc-new-york</t>
+  </si>
+  <si>
     <t>IT Support Consultancy</t>
   </si>
   <si>
     <t>Center for Transnational Environmental Accountability</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Civic Engagement, Climate Change, Environment</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ad8323da98c84a36b6959a499b9f63ab-it-support-consultancy-center-for-transnational-environmental-accountability-rockville</t>
+  </si>
+  <si>
+    <t>Jewish Life Associate</t>
+  </si>
+  <si>
+    <t>Sixth &amp; I</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc405587f97149a1b629bfc9235636cd-jewish-life-associate-sixth-i-washington</t>
+  </si>
+  <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN CALIFORNIA’S 48TH CONGRESSIONAL DISTRICT!</t>
+  </si>
+  <si>
+    <t>Worker Power</t>
+  </si>
+  <si>
+    <t>Palm Springs, California</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6f3fc460248436ea7e62d78bb76186a-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-palm-springs</t>
+  </si>
+  <si>
+    <t>Temecula, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8408a1c5154a40a5b46d76ead4e94a55-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-temecula</t>
+  </si>
+  <si>
+    <t>Literacy Tutor (PT, Temporary)</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71aa35fcbc0b430f8c54dfdb8cc10cac-literacy-tutor-pt-temporary-masa-bronx</t>
+  </si>
+  <si>
+    <t>Manager, Communications</t>
+  </si>
+  <si>
+    <t>Leading Edge</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 96000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e7d5690e489462aa81e705c28783cd7-manager-communications-leading-edge-new-york</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>Outreach Uganda</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7eabd2b967c64c7fb86f4aa7cb7717f1-marketing-community-engagement-manager-outreach-uganda-denver</t>
+  </si>
+  <si>
+    <t>Network Coordinator</t>
+  </si>
+  <si>
+    <t>Beyond100k</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2bb104fe46f4bcd9f4fb50f1cbcec21-network-coordinator-beyond100k-new-york</t>
+  </si>
+  <si>
+    <t>Operations Assistant #OPS#</t>
+  </si>
+  <si>
+    <t>Hotel and Gaming Trades Council, AFL-CIO</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66e07faaf65f4221b5467d81126059e6-operations-assistant-ops-hotel-and-gaming-trades-council-afl-cio-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Program Support Assistant</t>
+  </si>
+  <si>
+    <t>Fiesta Schoolyards LLC</t>
+  </si>
+  <si>
+    <t>Jenkintown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7682b22f1abc47aeafd0f51f0d349496-part-time-program-support-assistant-fiesta-schoolyards-llc-jenkintown</t>
+  </si>
+  <si>
+    <t>People &amp; Culture Officer (Talent, Performance &amp; Systems)</t>
+  </si>
+  <si>
+    <t>AVAAZ</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91954d6c93364bb3a0897c76f73881d1-people-culture-officer-talent-performance-systems-avaaz-london</t>
+  </si>
+  <si>
+    <t>Policy Assistant &amp; Paralegal</t>
+  </si>
+  <si>
+    <t>Lambda Legal</t>
+  </si>
+  <si>
+    <t>Washington D.C., District of Columbia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f646b72337944381acb420e2caa7d25f-policy-assistant-paralegal-lambda-legal-washington-dc</t>
+  </si>
+  <si>
+    <t>Polycapital Academy Lead</t>
+  </si>
+  <si>
+    <t>Regeneration Group (Generation Pledge)</t>
+  </si>
+  <si>
+    <t>USD 116482.34/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afcf4994c6ab41ba8019df19fc109095-polycapital-academy-lead-regeneration-group-generation-pledge-millburn</t>
+  </si>
+  <si>
+    <t>Posner Center Executive Director</t>
+  </si>
+  <si>
+    <t>Posner Center for International Development</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b565b36ac4064c4fb1bf3994eb827b28-posner-center-executive-director-posner-center-for-international-development-denver</t>
+  </si>
+  <si>
+    <t>Product Manager, Academy Products (Remote)</t>
+  </si>
+  <si>
+    <t>NAF</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13323ee69b7e4113891b99e807ed3deb-product-manager-academy-products-remote-naf-new-york</t>
+  </si>
+  <si>
+    <t>Product Manager, Expansion Products (Remote)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/452989a2e94547e0b9870821594046ba-product-manager-expansion-products-remote-naf-new-york</t>
+  </si>
+  <si>
+    <t>Program Assistant, Education</t>
+  </si>
+  <si>
+    <t>YIVO Institute for Jewish Research</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41c9da50b45c4ff5b63437a42c74565e-program-assistant-education-yivo-institute-for-jewish-research-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate</t>
+  </si>
+  <si>
+    <t>Bread &amp; Roses Community Fund</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 56122.00 - 62358.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a3e1749b3e34761bed2cabd1ad87aae-program-associate-bread-roses-community-fund-philadelphia</t>
+  </si>
+  <si>
+    <t>Program Coordinator - ROSES Advocacy Coordinator (Full-Time)</t>
+  </si>
+  <si>
+    <t>New York University - IHDSC</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d1d24bba5c24525b299b86f910a6207-program-coordinator-roses-advocacy-coordinator-full-time-new-york-university-ihdsc-new-york</t>
+  </si>
+  <si>
+    <t>Program Officer, Racial Equity and Community Engagement</t>
+  </si>
+  <si>
+    <t>W.K. Kellogg Foundation</t>
+  </si>
+  <si>
+    <t>Battle Creek, Michigan</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 181000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Family, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7e5ee96566334ffc8fae802ae2f06de6-program-officer-racial-equity-and-community-engagement-wk-kellogg-foundation-battle-creek</t>
+  </si>
+  <si>
+    <t>Programme Officer, Operations</t>
+  </si>
+  <si>
+    <t>ARTICLE 19</t>
+  </si>
+  <si>
+    <t>London, England, GB</t>
+  </si>
+  <si>
+    <t>GBP 46900.00 - 46900.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b0e894da9d14495a03a8ab78a5909bf-programme-officer-operations-article-19-london</t>
+  </si>
+  <si>
+    <t>Project Coordinator/Assistant</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/39838ec3b79d408896f0716b4aa5c5c0-project-coordinatorassistant-isaacson-miller-boston</t>
+  </si>
+  <si>
+    <t>Redevelopment Project Manager</t>
+  </si>
+  <si>
+    <t>Brookline Housing Authority</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/37500d92474d41cdb10aeade16cd09b4-redevelopment-project-manager-brookline-housing-authority-brookline</t>
+  </si>
+  <si>
+    <t>Residence Director (Prospect Park YMCA)</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 89100.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87ce1408a24d45a39cc3851f0ccf75f4-residence-director-prospect-park-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Salesforce Enablement Manager</t>
+  </si>
+  <si>
+    <t>Shatterproof</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db0b1e98ae8046a78b3fbf8481d4feb8-salesforce-enablement-manager-shatterproof-norwalk</t>
+  </si>
+  <si>
+    <t>Senior Development Manager</t>
+  </si>
+  <si>
+    <t>The Acceleration Project</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94b0bf4b2195459badbc172d810b3155-senior-development-manager-the-acceleration-project-scarsdale</t>
+  </si>
+  <si>
+    <t>Senior Director of Operations</t>
+  </si>
+  <si>
+    <t>Marine Corps University Foundation</t>
+  </si>
+  <si>
+    <t>Quantico, Virginia</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f167b637a254411b96f3dd30ca520329-senior-director-of-operations-marine-corps-university-foundation-quantico</t>
+  </si>
+  <si>
+    <t>Senior Manager, Salesforce &amp; Technology</t>
+  </si>
+  <si>
+    <t>U.S. Soccer Foundation</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c334e63fdca4e6bb320100ea849be77-senior-manager-salesforce-technology-us-soccer-foundation-washington</t>
+  </si>
+  <si>
+    <t>Senior Officer US Media</t>
+  </si>
+  <si>
+    <t>Helen Keller Intl</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50345f241f98421fa9cb6c936abf8d45-senior-officer-us-media-helen-keller-intl-new-york</t>
+  </si>
+  <si>
+    <t>Senior Project Manager, Real Estate</t>
+  </si>
+  <si>
+    <t>North Shore Community Development Coalition Inc.</t>
+  </si>
+  <si>
+    <t>Salem, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/260ef6fd54b34d349856ba4bfc587788-senior-project-manager-real-estate-north-shore-community-development-coalition-inc-salem</t>
+  </si>
+  <si>
+    <t>Social Media Manager</t>
+  </si>
+  <si>
+    <t>Chesapeake Climate Action Network</t>
+  </si>
+  <si>
+    <t>Takoma Park, Maryland</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85a8a20f0f014a60bc7e1956d6216bf9-social-media-manager-chesapeake-climate-action-network-takoma-park</t>
+  </si>
+  <si>
+    <t>Software Engineer (Early Career)</t>
+  </si>
+  <si>
+    <t>Constructive Dialogue Institute</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6965cacf0cf845ffaaae044a336111ec-software-engineer-early-career-constructive-dialogue-institute-new-york</t>
+  </si>
+  <si>
+    <t>Special Projects Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ccef15c71a541598d270ebb6f40e281-special-projects-manager-onja-toamasina</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>USD 84718.44/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc124bae96384cfaa6e9f1e0649c645b-staff-attorney-immigrant-legal-resource-center-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1df15c378b5e4d10bbf646f48fc1f289-staff-attorney-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Staff Attorney, affirmative immigration</t>
+  </si>
+  <si>
+    <t>Oasis Legal Services</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be0de6b341474612b429b83e8a41741b-staff-attorney-affirmative-immigration-oasis-legal-services-berkeley</t>
+  </si>
+  <si>
+    <t>Staff Attorney, removal defense</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3364612ad5314a3cacda6723831fb4fa-staff-attorney-removal-defense-oasis-legal-services-berkeley</t>
+  </si>
+  <si>
+    <t>Student Advisor</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fc7072fc41d43fdb571246cd70b200f-student-advisor-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Therapist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87d78281231b4145b45af44dd4ddfb93-therapist-onja-toamasina</t>
+  </si>
+  <si>
+    <t>Training &amp; Curriculum Lead</t>
+  </si>
+  <si>
+    <t>Rockwood Leadership Institute</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1511689108d4adaaba30d9222fb488c-training-curriculum-lead-rockwood-leadership-institute-san-francisco</t>
+  </si>
+  <si>
+    <t>Trial Attorney - Tenant Rights / Eviction Defense</t>
+  </si>
+  <si>
+    <t>BASTA Universal!</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60717b2a8fa9455da01a323b23ab8bd9-trial-attorney-tenant-rights-eviction-defense-basta-universal-los-angeles</t>
+  </si>
+  <si>
+    <t>Volunteer Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Bainbridge Prepares</t>
+  </si>
+  <si>
+    <t>Bainbridge Island, Washington</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff51876f36214eb89ba0bdf05d928ed8-volunteer-engagement-coordinator-bainbridge-prepares-bainbridge-island</t>
+  </si>
+  <si>
+    <t>Youth Coach/Trainer (Park Slope Armory YMCA)</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9bde912364d4bdc993c343a30a3d4b0-youth-coachtrainer-park-slope-armory-ymca-ymca-of-greater-new-york-kings-county</t>
   </si>
 </sst>
 </file>
@@ -573,7 +2193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -683,94 +2303,692 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E11" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>155</v>
+      </c>
+      <c r="F31" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>156</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" t="s">
+        <v>156</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
+        <v>167</v>
+      </c>
+      <c r="D34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>168</v>
+      </c>
+      <c r="F34" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -783,6 +3001,32 @@
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
     <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -791,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -830,8 +3074,106 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" t="s">
+        <v>190</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -839,7 +3181,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -880,31 +3222,1999 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>57</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" t="s">
+        <v>239</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11" t="s">
+        <v>249</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E13" t="s">
+        <v>255</v>
+      </c>
+      <c r="F13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" t="s">
+        <v>195</v>
+      </c>
+      <c r="E15" t="s">
+        <v>267</v>
+      </c>
+      <c r="F15" t="s">
+        <v>268</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" t="s">
+        <v>260</v>
+      </c>
+      <c r="D16" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" t="s">
+        <v>273</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" t="s">
+        <v>214</v>
+      </c>
+      <c r="E17" t="s">
+        <v>278</v>
+      </c>
+      <c r="F17" t="s">
+        <v>279</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" t="s">
+        <v>283</v>
+      </c>
+      <c r="F18" t="s">
+        <v>284</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" t="s">
+        <v>288</v>
+      </c>
+      <c r="D19" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" t="s">
+        <v>290</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" t="s">
+        <v>294</v>
+      </c>
+      <c r="D20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" t="s">
+        <v>296</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" t="s">
+        <v>301</v>
+      </c>
+      <c r="F21" t="s">
+        <v>302</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" t="s">
+        <v>305</v>
+      </c>
+      <c r="C22" t="s">
+        <v>294</v>
+      </c>
+      <c r="D22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" t="s">
+        <v>306</v>
+      </c>
+      <c r="F22" t="s">
+        <v>227</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>304</v>
+      </c>
+      <c r="B23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" t="s">
+        <v>309</v>
+      </c>
+      <c r="D23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" t="s">
+        <v>310</v>
+      </c>
+      <c r="F23" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>313</v>
+      </c>
+      <c r="B24" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" t="s">
+        <v>315</v>
+      </c>
+      <c r="D24" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" t="s">
+        <v>316</v>
+      </c>
+      <c r="F24" t="s">
+        <v>317</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" t="s">
+        <v>220</v>
+      </c>
+      <c r="D25" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" t="s">
+        <v>320</v>
+      </c>
+      <c r="F25" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B26" t="s">
+        <v>323</v>
+      </c>
+      <c r="C26" t="s">
+        <v>294</v>
+      </c>
+      <c r="D26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" t="s">
+        <v>324</v>
+      </c>
+      <c r="F26" t="s">
+        <v>325</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>327</v>
+      </c>
+      <c r="B27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C27" t="s">
+        <v>329</v>
+      </c>
+      <c r="D27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" t="s">
+        <v>330</v>
+      </c>
+      <c r="F27" t="s">
+        <v>331</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>333</v>
+      </c>
+      <c r="B28" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" t="s">
+        <v>335</v>
+      </c>
+      <c r="E28" t="s">
+        <v>336</v>
+      </c>
+      <c r="F28" t="s">
+        <v>337</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B29" t="s">
+        <v>340</v>
+      </c>
+      <c r="C29" t="s">
+        <v>341</v>
+      </c>
+      <c r="D29" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" t="s">
+        <v>227</v>
+      </c>
+      <c r="F29" t="s">
+        <v>342</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B30" t="s">
+        <v>345</v>
+      </c>
+      <c r="C30" t="s">
+        <v>346</v>
+      </c>
+      <c r="D30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" t="s">
+        <v>347</v>
+      </c>
+      <c r="F30" t="s">
+        <v>348</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>350</v>
+      </c>
+      <c r="B31" t="s">
+        <v>351</v>
+      </c>
+      <c r="C31" t="s">
+        <v>294</v>
+      </c>
+      <c r="D31" t="s">
+        <v>352</v>
+      </c>
+      <c r="E31" t="s">
+        <v>353</v>
+      </c>
+      <c r="F31" t="s">
+        <v>354</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>356</v>
+      </c>
+      <c r="B32" t="s">
+        <v>357</v>
+      </c>
+      <c r="C32" t="s">
+        <v>358</v>
+      </c>
+      <c r="D32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" t="s">
+        <v>359</v>
+      </c>
+      <c r="F32" t="s">
+        <v>360</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>362</v>
+      </c>
+      <c r="B33" t="s">
+        <v>363</v>
+      </c>
+      <c r="C33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" t="s">
+        <v>364</v>
+      </c>
+      <c r="F33" t="s">
+        <v>365</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>367</v>
+      </c>
+      <c r="B34" t="s">
+        <v>368</v>
+      </c>
+      <c r="C34" t="s">
+        <v>369</v>
+      </c>
+      <c r="D34" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" t="s">
+        <v>370</v>
+      </c>
+      <c r="F34" t="s">
+        <v>371</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>373</v>
+      </c>
+      <c r="B35" t="s">
+        <v>259</v>
+      </c>
+      <c r="C35" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" t="s">
+        <v>374</v>
+      </c>
+      <c r="F35" t="s">
+        <v>262</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>376</v>
+      </c>
+      <c r="B36" t="s">
+        <v>377</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" t="s">
+        <v>378</v>
+      </c>
+      <c r="F36" t="s">
+        <v>379</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>381</v>
+      </c>
+      <c r="B37" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" t="s">
+        <v>227</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>383</v>
+      </c>
+      <c r="B38" t="s">
+        <v>384</v>
+      </c>
+      <c r="C38" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" t="s">
+        <v>385</v>
+      </c>
+      <c r="F38" t="s">
+        <v>386</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>388</v>
+      </c>
+      <c r="B39" t="s">
+        <v>389</v>
+      </c>
+      <c r="C39" t="s">
+        <v>294</v>
+      </c>
+      <c r="D39" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" t="s">
+        <v>390</v>
+      </c>
+      <c r="F39" t="s">
+        <v>227</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>392</v>
+      </c>
+      <c r="B40" t="s">
+        <v>393</v>
+      </c>
+      <c r="C40" t="s">
+        <v>294</v>
+      </c>
+      <c r="D40" t="s">
+        <v>195</v>
+      </c>
+      <c r="E40" t="s">
+        <v>394</v>
+      </c>
+      <c r="F40" t="s">
+        <v>395</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B41" t="s">
+        <v>398</v>
+      </c>
+      <c r="C41" t="s">
+        <v>294</v>
+      </c>
+      <c r="D41" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" t="s">
+        <v>399</v>
+      </c>
+      <c r="F41" t="s">
+        <v>284</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>401</v>
+      </c>
+      <c r="B42" t="s">
+        <v>402</v>
+      </c>
+      <c r="C42" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" t="s">
+        <v>335</v>
+      </c>
+      <c r="E42" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" t="s">
+        <v>403</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>405</v>
+      </c>
+      <c r="B43" t="s">
+        <v>406</v>
+      </c>
+      <c r="C43" t="s">
+        <v>407</v>
+      </c>
+      <c r="D43" t="s">
+        <v>195</v>
+      </c>
+      <c r="E43" t="s">
+        <v>408</v>
+      </c>
+      <c r="F43" t="s">
+        <v>409</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>411</v>
+      </c>
+      <c r="B44" t="s">
+        <v>412</v>
+      </c>
+      <c r="C44" t="s">
+        <v>413</v>
+      </c>
+      <c r="D44" t="s">
+        <v>352</v>
+      </c>
+      <c r="E44" t="s">
+        <v>414</v>
+      </c>
+      <c r="F44" t="s">
+        <v>415</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>411</v>
+      </c>
+      <c r="B45" t="s">
+        <v>412</v>
+      </c>
+      <c r="C45" t="s">
+        <v>417</v>
+      </c>
+      <c r="D45" t="s">
+        <v>352</v>
+      </c>
+      <c r="E45" t="s">
+        <v>414</v>
+      </c>
+      <c r="F45" t="s">
+        <v>415</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>419</v>
+      </c>
+      <c r="B46" t="s">
+        <v>420</v>
+      </c>
+      <c r="C46" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" t="s">
+        <v>421</v>
+      </c>
+      <c r="E46" t="s">
+        <v>422</v>
+      </c>
+      <c r="F46" t="s">
+        <v>423</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>425</v>
+      </c>
+      <c r="B47" t="s">
+        <v>426</v>
+      </c>
+      <c r="C47" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" t="s">
+        <v>427</v>
+      </c>
+      <c r="F47" t="s">
+        <v>428</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>430</v>
+      </c>
+      <c r="B48" t="s">
+        <v>431</v>
+      </c>
+      <c r="C48" t="s">
+        <v>432</v>
+      </c>
+      <c r="D48" t="s">
+        <v>214</v>
+      </c>
+      <c r="E48" t="s">
+        <v>422</v>
+      </c>
+      <c r="F48" t="s">
+        <v>433</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>435</v>
+      </c>
+      <c r="B49" t="s">
+        <v>436</v>
+      </c>
+      <c r="C49" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" t="s">
+        <v>437</v>
+      </c>
+      <c r="F49" t="s">
+        <v>438</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>440</v>
+      </c>
+      <c r="B50" t="s">
+        <v>441</v>
+      </c>
+      <c r="C50" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" t="s">
+        <v>195</v>
+      </c>
+      <c r="E50" t="s">
+        <v>442</v>
+      </c>
+      <c r="F50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>444</v>
+      </c>
+      <c r="B51" t="s">
+        <v>445</v>
+      </c>
+      <c r="C51" t="s">
+        <v>446</v>
+      </c>
+      <c r="D51" t="s">
+        <v>214</v>
+      </c>
+      <c r="E51" t="s">
+        <v>447</v>
+      </c>
+      <c r="F51" t="s">
+        <v>448</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>450</v>
+      </c>
+      <c r="B52" t="s">
+        <v>451</v>
+      </c>
+      <c r="C52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" t="s">
+        <v>195</v>
+      </c>
+      <c r="E52" t="s">
+        <v>227</v>
+      </c>
+      <c r="F52" t="s">
+        <v>452</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>454</v>
+      </c>
+      <c r="B53" t="s">
+        <v>455</v>
+      </c>
+      <c r="C53" t="s">
+        <v>456</v>
+      </c>
+      <c r="D53" t="s">
+        <v>195</v>
+      </c>
+      <c r="E53" t="s">
+        <v>227</v>
+      </c>
+      <c r="F53" t="s">
+        <v>227</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>458</v>
+      </c>
+      <c r="B54" t="s">
+        <v>459</v>
+      </c>
+      <c r="C54" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" t="s">
+        <v>335</v>
+      </c>
+      <c r="E54" t="s">
+        <v>460</v>
+      </c>
+      <c r="F54" t="s">
+        <v>461</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>463</v>
+      </c>
+      <c r="B55" t="s">
+        <v>464</v>
+      </c>
+      <c r="C55" t="s">
+        <v>432</v>
+      </c>
+      <c r="D55" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55" t="s">
+        <v>465</v>
+      </c>
+      <c r="F55" t="s">
+        <v>466</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>468</v>
+      </c>
+      <c r="B56" t="s">
+        <v>469</v>
+      </c>
+      <c r="C56" t="s">
+        <v>178</v>
+      </c>
+      <c r="D56" t="s">
+        <v>195</v>
+      </c>
+      <c r="E56" t="s">
+        <v>470</v>
+      </c>
+      <c r="F56" t="s">
+        <v>296</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>472</v>
+      </c>
+      <c r="B57" t="s">
+        <v>469</v>
+      </c>
+      <c r="C57" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" t="s">
+        <v>195</v>
+      </c>
+      <c r="E57" t="s">
+        <v>470</v>
+      </c>
+      <c r="F57" t="s">
+        <v>296</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>474</v>
+      </c>
+      <c r="B58" t="s">
+        <v>475</v>
+      </c>
+      <c r="C58" t="s">
+        <v>294</v>
+      </c>
+      <c r="D58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" t="s">
+        <v>476</v>
+      </c>
+      <c r="F58" t="s">
+        <v>477</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>479</v>
+      </c>
+      <c r="B59" t="s">
+        <v>480</v>
+      </c>
+      <c r="C59" t="s">
+        <v>481</v>
+      </c>
+      <c r="D59" t="s">
+        <v>195</v>
+      </c>
+      <c r="E59" t="s">
+        <v>482</v>
+      </c>
+      <c r="F59" t="s">
+        <v>483</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>485</v>
+      </c>
+      <c r="B60" t="s">
+        <v>486</v>
+      </c>
+      <c r="C60" t="s">
+        <v>294</v>
+      </c>
+      <c r="D60" t="s">
+        <v>195</v>
+      </c>
+      <c r="E60" t="s">
+        <v>310</v>
+      </c>
+      <c r="F60" t="s">
+        <v>487</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>489</v>
+      </c>
+      <c r="B61" t="s">
+        <v>490</v>
+      </c>
+      <c r="C61" t="s">
+        <v>491</v>
+      </c>
+      <c r="D61" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" t="s">
+        <v>492</v>
+      </c>
+      <c r="F61" t="s">
+        <v>493</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>495</v>
+      </c>
+      <c r="B62" t="s">
+        <v>496</v>
+      </c>
+      <c r="C62" t="s">
+        <v>497</v>
+      </c>
+      <c r="D62" t="s">
+        <v>352</v>
+      </c>
+      <c r="E62" t="s">
+        <v>498</v>
+      </c>
+      <c r="F62" t="s">
+        <v>499</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>501</v>
+      </c>
+      <c r="B63" t="s">
+        <v>384</v>
+      </c>
+      <c r="C63" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" t="s">
+        <v>195</v>
+      </c>
+      <c r="E63" t="s">
+        <v>502</v>
+      </c>
+      <c r="F63" t="s">
+        <v>503</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>505</v>
+      </c>
+      <c r="B64" t="s">
+        <v>506</v>
+      </c>
+      <c r="C64" t="s">
+        <v>507</v>
+      </c>
+      <c r="D64" t="s">
+        <v>195</v>
+      </c>
+      <c r="E64" t="s">
+        <v>508</v>
+      </c>
+      <c r="F64" t="s">
+        <v>509</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>511</v>
+      </c>
+      <c r="B65" t="s">
+        <v>259</v>
+      </c>
+      <c r="C65" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" t="s">
+        <v>512</v>
+      </c>
+      <c r="F65" t="s">
+        <v>513</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>515</v>
+      </c>
+      <c r="B66" t="s">
+        <v>516</v>
+      </c>
+      <c r="C66" t="s">
+        <v>178</v>
+      </c>
+      <c r="D66" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" t="s">
+        <v>517</v>
+      </c>
+      <c r="F66" t="s">
+        <v>518</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>520</v>
+      </c>
+      <c r="B67" t="s">
+        <v>521</v>
+      </c>
+      <c r="C67" t="s">
+        <v>522</v>
+      </c>
+      <c r="D67" t="s">
+        <v>195</v>
+      </c>
+      <c r="E67" t="s">
+        <v>272</v>
+      </c>
+      <c r="F67" t="s">
+        <v>523</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>525</v>
+      </c>
+      <c r="B68" t="s">
+        <v>526</v>
+      </c>
+      <c r="C68" t="s">
+        <v>527</v>
+      </c>
+      <c r="D68" t="s">
+        <v>195</v>
+      </c>
+      <c r="E68" t="s">
+        <v>528</v>
+      </c>
+      <c r="F68" t="s">
+        <v>529</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>531</v>
+      </c>
+      <c r="B69" t="s">
+        <v>532</v>
+      </c>
+      <c r="C69" t="s">
+        <v>178</v>
+      </c>
+      <c r="D69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" t="s">
+        <v>533</v>
+      </c>
+      <c r="F69" t="s">
+        <v>279</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>535</v>
+      </c>
+      <c r="B70" t="s">
+        <v>536</v>
+      </c>
+      <c r="C70" t="s">
+        <v>522</v>
+      </c>
+      <c r="D70" t="s">
+        <v>195</v>
+      </c>
+      <c r="E70" t="s">
+        <v>227</v>
+      </c>
+      <c r="F70" t="s">
+        <v>537</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>539</v>
+      </c>
+      <c r="B71" t="s">
+        <v>540</v>
+      </c>
+      <c r="C71" t="s">
+        <v>541</v>
+      </c>
+      <c r="D71" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" t="s">
+        <v>542</v>
+      </c>
+      <c r="F71" t="s">
+        <v>487</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>544</v>
+      </c>
+      <c r="B72" t="s">
+        <v>545</v>
+      </c>
+      <c r="C72" t="s">
+        <v>546</v>
+      </c>
+      <c r="D72" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" t="s">
+        <v>547</v>
+      </c>
+      <c r="F72" t="s">
+        <v>548</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>550</v>
+      </c>
+      <c r="B73" t="s">
+        <v>551</v>
+      </c>
+      <c r="C73" t="s">
+        <v>178</v>
+      </c>
+      <c r="D73" t="s">
+        <v>195</v>
+      </c>
+      <c r="E73" t="s">
+        <v>552</v>
+      </c>
+      <c r="F73" t="s">
+        <v>553</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>555</v>
+      </c>
+      <c r="B74" t="s">
+        <v>225</v>
+      </c>
+      <c r="C74" t="s">
+        <v>226</v>
+      </c>
+      <c r="D74" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" t="s">
+        <v>227</v>
+      </c>
+      <c r="F74" t="s">
+        <v>227</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>557</v>
+      </c>
+      <c r="B75" t="s">
+        <v>558</v>
+      </c>
+      <c r="C75" t="s">
+        <v>358</v>
+      </c>
+      <c r="D75" t="s">
+        <v>195</v>
+      </c>
+      <c r="E75" t="s">
+        <v>559</v>
+      </c>
+      <c r="F75" t="s">
+        <v>560</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>557</v>
+      </c>
+      <c r="B76" t="s">
+        <v>558</v>
+      </c>
+      <c r="C76" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" t="s">
+        <v>195</v>
+      </c>
+      <c r="E76" t="s">
+        <v>559</v>
+      </c>
+      <c r="F76" t="s">
+        <v>560</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>563</v>
+      </c>
+      <c r="B77" t="s">
+        <v>564</v>
+      </c>
+      <c r="C77" t="s">
+        <v>565</v>
+      </c>
+      <c r="D77" t="s">
+        <v>195</v>
+      </c>
+      <c r="E77" t="s">
+        <v>566</v>
+      </c>
+      <c r="F77" t="s">
+        <v>567</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>569</v>
+      </c>
+      <c r="B78" t="s">
+        <v>564</v>
+      </c>
+      <c r="C78" t="s">
+        <v>565</v>
+      </c>
+      <c r="D78" t="s">
+        <v>195</v>
+      </c>
+      <c r="E78" t="s">
+        <v>566</v>
+      </c>
+      <c r="F78" t="s">
+        <v>567</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>571</v>
+      </c>
+      <c r="B79" t="s">
+        <v>572</v>
+      </c>
+      <c r="C79" t="s">
+        <v>282</v>
+      </c>
+      <c r="D79" t="s">
+        <v>195</v>
+      </c>
+      <c r="E79" t="s">
+        <v>573</v>
+      </c>
+      <c r="F79" t="s">
+        <v>574</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>576</v>
+      </c>
+      <c r="B80" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" t="s">
+        <v>195</v>
+      </c>
+      <c r="E80" t="s">
+        <v>227</v>
+      </c>
+      <c r="F80" t="s">
+        <v>227</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>578</v>
+      </c>
+      <c r="B81" t="s">
+        <v>579</v>
+      </c>
+      <c r="C81" t="s">
+        <v>178</v>
+      </c>
+      <c r="D81" t="s">
+        <v>195</v>
+      </c>
+      <c r="E81" t="s">
+        <v>580</v>
+      </c>
+      <c r="F81" t="s">
+        <v>581</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>583</v>
+      </c>
+      <c r="B82" t="s">
+        <v>584</v>
+      </c>
+      <c r="C82" t="s">
+        <v>585</v>
+      </c>
+      <c r="D82" t="s">
+        <v>195</v>
+      </c>
+      <c r="E82" t="s">
+        <v>586</v>
+      </c>
+      <c r="F82" t="s">
+        <v>587</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>589</v>
+      </c>
+      <c r="B83" t="s">
+        <v>590</v>
+      </c>
+      <c r="C83" t="s">
+        <v>591</v>
+      </c>
+      <c r="D83" t="s">
+        <v>214</v>
+      </c>
+      <c r="E83" t="s">
+        <v>592</v>
+      </c>
+      <c r="F83" t="s">
+        <v>593</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>595</v>
+      </c>
+      <c r="B84" t="s">
+        <v>259</v>
+      </c>
+      <c r="C84" t="s">
+        <v>260</v>
+      </c>
+      <c r="D84" t="s">
+        <v>214</v>
+      </c>
+      <c r="E84" t="s">
+        <v>596</v>
+      </c>
+      <c r="F84" t="s">
+        <v>262</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-13.xlsx
+++ b/docs/xlsx/jobs-2026-10-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="739">
   <si>
     <t>Title</t>
   </si>
@@ -613,6 +613,99 @@
     <t>https://www.idealist.org/en/nonprofit-job/a04bf96ff9ee4dffbcc2397a6492e895-advocacy-specialist-treaty-bodies-ilga-world-the-international-lesbian-gay-bisexual-trans-and-intersex-association-geneva</t>
   </si>
   <si>
+    <t>Associate Attorney</t>
+  </si>
+  <si>
+    <t>Correia &amp; Puth, PLLC</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/7c441cf62cea42939040465a9aab914a-associate-attorney-correia-puth-pllc-washington</t>
+  </si>
+  <si>
+    <t>Business Development Director</t>
+  </si>
+  <si>
+    <t>Japanese American Citizens League</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Race Ethnicity, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f467e5badd4d4ebca2debdc8d18e91c1-business-development-director-japanese-american-citizens-league-san-francisco</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b7820eaf386e4bf49c28512091e9797f-business-development-director-japanese-american-citizens-league-los-angeles</t>
+  </si>
+  <si>
+    <t>Business Operations Lead</t>
+  </si>
+  <si>
+    <t>Berkeley Food Network</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff24c0f1c0cb4ab58837eecf6d8f5025-business-operations-lead-berkeley-food-network-berkeley</t>
+  </si>
+  <si>
+    <t>Campaign Manager, Food Safety</t>
+  </si>
+  <si>
+    <t>Center for Science in the Public Interest</t>
+  </si>
+  <si>
+    <t>USD 94000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/630c6dfcf9694e0b9f4c6abd9b1d2212-campaign-manager-food-safety-center-for-science-in-the-public-interest-washington</t>
+  </si>
+  <si>
+    <t>Campaign Organizer - Denver</t>
+  </si>
+  <si>
+    <t>The Redress Movement</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4d8fcf6c01b414f9c7b0ce6862b0b5e-campaign-organizer-denver-the-redress-movement-denver</t>
+  </si>
+  <si>
     <t>Chief Executive Officer</t>
   </si>
   <si>
@@ -649,6 +742,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/33ab1d9138b14e27a2512492f66d3c9c-chief-financial-officer-homefront-mercer-county-nj-lawrence-township</t>
   </si>
   <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Cayton Children's Museum</t>
+  </si>
+  <si>
+    <t>Santa Monica, California</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4a3a6be14b44718a7c35242abcee31b-chief-operating-officer-cayton-childrens-museum-santa-monica</t>
+  </si>
+  <si>
     <t>Client Assistant</t>
   </si>
   <si>
@@ -841,6 +952,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9aca6b09c8a941b59ce05aef2ffb5f06-day-camp-director-trail-blazers-kings-county</t>
   </si>
   <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>WE CAN</t>
+  </si>
+  <si>
+    <t>Harwich, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Legal Assistance, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b904fa587b7e410f83c725a685e73161-development-coordinator-we-can-harwich</t>
+  </si>
+  <si>
     <t>Development Director</t>
   </si>
   <si>
@@ -880,9 +1009,6 @@
     <t>Build Health International</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 120000.00/year</t>
   </si>
   <si>
@@ -892,6 +1018,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9c91335ad14d460d8765fd260a7226d2-development-officer-west-coast-build-health-international-san-francisco</t>
   </si>
   <si>
+    <t>Direct Support Professional with a Focus on Communication</t>
+  </si>
+  <si>
+    <t>Carousel Connections, LLC</t>
+  </si>
+  <si>
+    <t>Ardmore, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 61400.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/50242b97498b403db6006aac845ce1fd-direct-support-professional-with-a-focus-on-communication-carousel-connections-llc-ardmore</t>
+  </si>
+  <si>
     <t>Director - New York</t>
   </si>
   <si>
@@ -955,6 +1099,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/974dcc1fabd14bee8168debd81b7ad7a-director-of-development-park-city-conservation-association-dba-recycle-utah-park-city</t>
   </si>
   <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Infant/Child Enrichment Services (ICES)</t>
+  </si>
+  <si>
+    <t>Sonora, California</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6105598012c54c6a826c143d411b309f-director-of-finance-infantchild-enrichment-services-ices-sonora</t>
+  </si>
+  <si>
+    <t>The Acceleration Project</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1327d4cc479a4b57b462b0af8108d6b2-director-of-finance-the-acceleration-project-scarsdale</t>
+  </si>
+  <si>
+    <t>Director of Human Resources and Culture</t>
+  </si>
+  <si>
+    <t>Homebase</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1d13db12c824e6f847fcff2f39dd5a4-director-of-human-resources-and-culture-homebase-san-francisco</t>
+  </si>
+  <si>
     <t>Director of Resource Development</t>
   </si>
   <si>
@@ -964,9 +1156,6 @@
     <t>Chelsea, Massachusetts</t>
   </si>
   <si>
-    <t>USD 140000.00 - 155000.00/year</t>
-  </si>
-  <si>
     <t>Community Development, Housing Homelessness, Human Rights Civil Liberties</t>
   </si>
   <si>
@@ -1033,6 +1222,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/cdeba5d720ed4ea48af336fd1da88297-end-of-year-campaign-manager-elba-hope-foundation-new-york</t>
   </si>
   <si>
+    <t>Enrollment &amp; Operations Coordinator (Bookkeeper) (Japanese-speaking)</t>
+  </si>
+  <si>
+    <t>Aozora Community Foundation</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c88f531b3084158bce023ec23112e34-enrollment-operations-coordinator-bookkeeper-japanese-speaking-aozora-community-foundation-kings-county</t>
+  </si>
+  <si>
     <t>Enrollment Operations Manager</t>
   </si>
   <si>
@@ -1102,6 +1306,21 @@
     <t>https://www.idealist.org/en/job/7f9e98a26c284e4692be3d5f99a0c390-executive-administrative-partner-agog-los-angeles</t>
   </si>
   <si>
+    <t>Longmont Public Media</t>
+  </si>
+  <si>
+    <t>Longmont, Colorado</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd14b90c4012469d87317ba36deb992b-executive-director-longmont-public-media-longmont</t>
+  </si>
+  <si>
     <t>Family Services Coordinator</t>
   </si>
   <si>
@@ -1144,6 +1363,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b4e706495c7a40e7bba9d2e78d5b539c-fitness-center-coach-park-slope-armory-ymca-ymca-of-greater-new-york-kings-county</t>
   </si>
   <si>
+    <t>Foundation Relations Officer</t>
+  </si>
+  <si>
+    <t>Center for Constitutional Rights</t>
+  </si>
+  <si>
+    <t>USD 122888.00 - 145520.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29dab5da2b1e46f4b864df901855a65e-foundation-relations-officer-center-for-constitutional-rights-new-york</t>
+  </si>
+  <si>
     <t>Grant Accountant</t>
   </si>
   <si>
@@ -1165,6 +1399,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7108ad7d6b234bb5b943685c5d060b15-growth-manager-onja-toamasina</t>
   </si>
   <si>
+    <t>Head of Programmes</t>
+  </si>
+  <si>
+    <t>SEED Madagascar</t>
+  </si>
+  <si>
+    <t>Taolagnaro, Anosy, MG</t>
+  </si>
+  <si>
+    <t>MGA 5000000.00 - 5000000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1fb9569b10be497193eea95e768942e3-head-of-programmes-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Healthcare Associate</t>
   </si>
   <si>
@@ -1219,6 +1471,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/ed6bfb0782f44d8396fddb65e934861d-individual-giving-manager-on-site-young-peoples-chorus-of-nyc-new-york</t>
   </si>
   <si>
+    <t>Intake Coordinator</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/67716c936db746829942117acaeb73b5-intake-coordinator-correia-puth-pllc-washington</t>
+  </si>
+  <si>
     <t>IT Support Consultancy</t>
   </si>
   <si>
@@ -1273,6 +1534,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/8408a1c5154a40a5b46d76ead4e94a55-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-temecula</t>
   </si>
   <si>
+    <t>Legal Secretary Manager (Stay Housed LA) - Support Services Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 82007.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f02628642c01452d9c2b012e52202262-legal-secretary-manager-stay-housed-la-support-services-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Literacy Tutor (PT, Temporary)</t>
   </si>
   <si>
@@ -1312,15 +1585,21 @@
     <t>Outreach Uganda</t>
   </si>
   <si>
-    <t>Denver, Colorado</t>
-  </si>
-  <si>
     <t>Education, Health Medicine, International Relations</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/7eabd2b967c64c7fb86f4aa7cb7717f1-marketing-community-engagement-manager-outreach-uganda-denver</t>
   </si>
   <si>
+    <t>Media and Communications Officer</t>
+  </si>
+  <si>
+    <t>MGA 1800000.00 - 1800000.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5be75cd3ee2a4b41b8ed7bf560218c09-media-and-communications-officer-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Network Coordinator</t>
   </si>
   <si>
@@ -1360,9 +1639,6 @@
     <t>USD 20.00/hour</t>
   </si>
   <si>
-    <t>Children Youth</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/7682b22f1abc47aeafd0f51f0d349496-part-time-program-support-assistant-fiesta-schoolyards-llc-jenkintown</t>
   </si>
   <si>
@@ -1378,6 +1654,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/91954d6c93364bb3a0897c76f73881d1-people-culture-officer-talent-performance-systems-avaaz-london</t>
   </si>
   <si>
+    <t>Philanthropic Services Operations Contractor</t>
+  </si>
+  <si>
+    <t>Assets Under Movement</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f69352a10092431eac3b3a8995cb9bef-philanthropic-services-operations-contractor-assets-under-movement-washington</t>
+  </si>
+  <si>
     <t>Policy Assistant &amp; Paralegal</t>
   </si>
   <si>
@@ -1420,6 +1711,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/b565b36ac4064c4fb1bf3994eb827b28-posner-center-executive-director-posner-center-for-international-development-denver</t>
   </si>
   <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>Reproductive Equity Now</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3ed97dc672e341099df8fd12267f2712-president-reproductive-equity-now-boston</t>
+  </si>
+  <si>
     <t>Product Manager, Academy Products (Remote)</t>
   </si>
   <si>
@@ -1501,6 +1804,39 @@
     <t>https://www.idealist.org/en/job/7e5ee96566334ffc8fae802ae2f06de6-program-officer-racial-equity-and-community-engagement-wk-kellogg-foundation-battle-creek</t>
   </si>
   <si>
+    <t>Program Supervisor Community Programs and Organizing</t>
+  </si>
+  <si>
+    <t>AT THE CROSSROADS</t>
+  </si>
+  <si>
+    <t>SAN FRANCISCO, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Civic Engagement, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3bb775f0f7f64541b3eb4c383e584513-program-supervisor-community-programs-and-organizing-at-the-crossroads-san-francisco</t>
+  </si>
+  <si>
+    <t>Programme Manager - Community Health</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8ca06bcca2f452398a510e23d37778d-programme-manager-community-health-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Programme Officer - Financial Resilience</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45f7a5fef9d84a8284fd04d0bc53e34f-programme-officer-financial-resilience-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Programme Officer, Operations</t>
   </si>
   <si>
@@ -1519,6 +1855,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/4b0e894da9d14495a03a8ab78a5909bf-programme-officer-operations-article-19-london</t>
   </si>
   <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>USD 52500.00 - 52500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/282fdcb6ca76413abe005f74eda9ff50-project-coordinator-fiesta-schoolyards-llc-jenkintown</t>
+  </si>
+  <si>
     <t>Project Coordinator/Assistant</t>
   </si>
   <si>
@@ -1531,6 +1879,21 @@
     <t>https://www.idealist.org/en/job/39838ec3b79d408896f0716b4aa5c5c0-project-coordinatorassistant-isaacson-miller-boston</t>
   </si>
   <si>
+    <t>Public Policy Coordinator</t>
+  </si>
+  <si>
+    <t>National Network to End Domestic Violence</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca91660966844b0694866f3da71878e4-public-policy-coordinator-national-network-to-end-domestic-violence-washington</t>
+  </si>
+  <si>
     <t>Redevelopment Project Manager</t>
   </si>
   <si>
@@ -1540,15 +1903,18 @@
     <t>Brookline, Massachusetts</t>
   </si>
   <si>
-    <t>USD 90000.00 - 110000.00/year</t>
-  </si>
-  <si>
     <t>Community Development, Housing Homelessness</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/government-job/37500d92474d41cdb10aeade16cd09b4-redevelopment-project-manager-brookline-housing-authority-brookline</t>
   </si>
   <si>
+    <t>Research &amp; Evaluation Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf45c6f7a6e04d35aeb00ffa58e2aaf7-research-evaluation-associate-the-episcopal-health-foundation-houston</t>
+  </si>
+  <si>
     <t>Residence Director (Prospect Park YMCA)</t>
   </si>
   <si>
@@ -1576,18 +1942,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/db0b1e98ae8046a78b3fbf8481d4feb8-salesforce-enablement-manager-shatterproof-norwalk</t>
   </si>
   <si>
+    <t>Seasonal Program Manager</t>
+  </si>
+  <si>
+    <t>Global Leadership Adventures</t>
+  </si>
+  <si>
+    <t>USD 36000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/dcb654121c7c4df5ae13e226e6d43c71-seasonal-program-manager-global-leadership-adventures-san-diego</t>
+  </si>
+  <si>
+    <t>Senior Conservation Research Assistant (Madagascar)</t>
+  </si>
+  <si>
+    <t>Environment, Community Development, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab63a30568874a51860e55c437d25c6b-senior-conservation-research-assistant-madagascar-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Senior Development Manager</t>
   </si>
   <si>
-    <t>The Acceleration Project</t>
-  </si>
-  <si>
-    <t>Remote (New York)</t>
-  </si>
-  <si>
-    <t>Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/94b0bf4b2195459badbc172d810b3155-senior-development-manager-the-acceleration-project-scarsdale</t>
   </si>
   <si>
@@ -1600,9 +1981,6 @@
     <t>Quantico, Virginia</t>
   </si>
   <si>
-    <t>USD 155000.00 - 175000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music, Children Youth, Community Development</t>
   </si>
   <si>
@@ -1657,9 +2035,6 @@
     <t>Takoma Park, Maryland</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Civic Engagement, Climate Change, Energy</t>
   </si>
   <si>
@@ -1705,15 +2080,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/1df15c378b5e4d10bbf646f48fc1f289-staff-attorney-immigrant-legal-resource-center-san-francisco</t>
   </si>
   <si>
+    <t>Staff Attorney King County Housing Justice Project</t>
+  </si>
+  <si>
+    <t>King County Bar Association, Seattle, WA</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 83230.00 - 116218.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c31677ea80543c68f38bd70d0a1c78c-staff-attorney-king-county-housing-justice-project-king-county-bar-association-seattle-wa-seattle</t>
+  </si>
+  <si>
     <t>Staff Attorney, affirmative immigration</t>
   </si>
   <si>
     <t>Oasis Legal Services</t>
   </si>
   <si>
-    <t>Berkeley, California</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 108000.00/year</t>
   </si>
   <si>
@@ -1744,6 +2134,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/2fc7072fc41d43fdb571246cd70b200f-student-advisor-east-side-house-settlement-bronx-county</t>
   </si>
   <si>
+    <t>Supervising Attorney – Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>USD 105174.00 - 123039.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3870ca12aa094787b2123205688ffee1-supervising-attorney-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Supervising Attorney and Coalition Director</t>
+  </si>
+  <si>
+    <t>National Immigration Project</t>
+  </si>
+  <si>
+    <t>USD 103646.00 - 126698.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0932f4dc416246f3967e0668ffe93acd-supervising-attorney-and-coalition-director-national-immigration-project-washington</t>
+  </si>
+  <si>
     <t>Therapist</t>
   </si>
   <si>
@@ -1771,18 +2185,30 @@
     <t>BASTA Universal!</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 120000.00/year</t>
   </si>
   <si>
-    <t>Housing Homelessness, Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/60717b2a8fa9455da01a323b23ab8bd9-trial-attorney-tenant-rights-eviction-defense-basta-universal-los-angeles</t>
   </si>
   <si>
+    <t>Visitor Services &amp; Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>DANIEL O MORRIS SOUTH CAROLINA LOW COUNTRY HERITAGE TR</t>
+  </si>
+  <si>
+    <t>Ridgeland, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d981e77d36cb405eb366b4a45fc00ece-visitor-services-volunteer-coordinator-daniel-o-morris-south-carolina-low-country-heritage-tr-ridgeland</t>
+  </si>
+  <si>
     <t>Volunteer Engagement Coordinator</t>
   </si>
   <si>
@@ -1802,9 +2228,6 @@
   </si>
   <si>
     <t>Youth Coach/Trainer (Park Slope Armory YMCA)</t>
-  </si>
-  <si>
-    <t>USD 25.00 - 25.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/b9bde912364d4bdc993c343a30a3d4b0-youth-coachtrainer-park-slope-armory-ymca-ymca-of-greater-new-york-kings-county</t>
@@ -3181,7 +3604,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3291,620 +3714,620 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" t="s">
         <v>211</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" t="s">
+        <v>209</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="C5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D5" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" t="s">
-        <v>216</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
         <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F7" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D8" t="s">
         <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D9" t="s">
         <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F9" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" t="s">
+        <v>239</v>
+      </c>
+      <c r="F10" t="s">
+        <v>240</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B10" t="s">
-        <v>242</v>
-      </c>
-      <c r="C10" t="s">
-        <v>243</v>
-      </c>
-      <c r="D10" t="s">
-        <v>195</v>
-      </c>
-      <c r="E10" t="s">
-        <v>244</v>
-      </c>
-      <c r="F10" t="s">
-        <v>227</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
         <v>246</v>
       </c>
-      <c r="B11" t="s">
+      <c r="H11" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D11" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" t="s">
-        <v>227</v>
-      </c>
-      <c r="F11" t="s">
-        <v>249</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" t="s">
         <v>251</v>
       </c>
-      <c r="B12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" t="s">
-        <v>195</v>
-      </c>
       <c r="E12" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="F12" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
         <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B15" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D15" t="s">
         <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
         <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F16" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D17" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F17" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="F18" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="D19" t="s">
         <v>195</v>
       </c>
       <c r="E19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F19" t="s">
+        <v>264</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="F19" t="s">
-        <v>290</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>290</v>
+      </c>
+      <c r="B20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" t="s">
         <v>292</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" t="s">
         <v>293</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E20" t="s">
-        <v>295</v>
-      </c>
-      <c r="F20" t="s">
-        <v>296</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" t="s">
         <v>298</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>299</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E21" t="s">
-        <v>301</v>
-      </c>
-      <c r="F21" t="s">
-        <v>302</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>301</v>
+      </c>
+      <c r="B22" t="s">
+        <v>302</v>
+      </c>
+      <c r="C22" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" t="s">
         <v>304</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>305</v>
       </c>
-      <c r="C22" t="s">
-        <v>294</v>
-      </c>
-      <c r="D22" t="s">
-        <v>195</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="H22" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="F22" t="s">
-        <v>227</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B23" t="s">
         <v>308</v>
       </c>
       <c r="C23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E23" t="s">
         <v>309</v>
       </c>
-      <c r="D23" t="s">
-        <v>195</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>310</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>312</v>
+      </c>
+      <c r="B24" t="s">
         <v>313</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>314</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" t="s">
         <v>315</v>
       </c>
-      <c r="D24" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>316</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" t="s">
         <v>319</v>
       </c>
-      <c r="B25" t="s">
-        <v>219</v>
-      </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="E25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F25" t="s">
-        <v>222</v>
+        <v>322</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B26" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C26" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="D26" t="s">
         <v>195</v>
       </c>
       <c r="E26" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F26" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B27" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C27" t="s">
-        <v>329</v>
+        <v>207</v>
       </c>
       <c r="D27" t="s">
         <v>195</v>
       </c>
       <c r="E27" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F27" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B28" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>336</v>
       </c>
       <c r="D28" t="s">
-        <v>335</v>
+        <v>195</v>
       </c>
       <c r="E28" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D29" t="s">
         <v>195</v>
       </c>
       <c r="E29" t="s">
-        <v>227</v>
+        <v>343</v>
       </c>
       <c r="F29" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B30" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D30" t="s">
         <v>195</v>
       </c>
       <c r="E30" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F30" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B31" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C31" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="D31" t="s">
-        <v>352</v>
+        <v>195</v>
       </c>
       <c r="E31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F31" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>355</v>
@@ -3912,36 +4335,36 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>352</v>
+      </c>
+      <c r="B32" t="s">
         <v>356</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>357</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" t="s">
         <v>358</v>
       </c>
-      <c r="D32" t="s">
-        <v>195</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>359</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B33" t="s">
         <v>362</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>363</v>
-      </c>
-      <c r="C33" t="s">
-        <v>294</v>
       </c>
       <c r="D33" t="s">
         <v>195</v>
@@ -3958,919 +4381,919 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>361</v>
+      </c>
+      <c r="B34" t="s">
         <v>367</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>368</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" t="s">
         <v>369</v>
       </c>
-      <c r="D34" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>370</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>372</v>
+      </c>
+      <c r="B35" t="s">
         <v>373</v>
       </c>
-      <c r="B35" t="s">
-        <v>259</v>
-      </c>
       <c r="C35" t="s">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
         <v>374</v>
       </c>
       <c r="F35" t="s">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>379</v>
       </c>
       <c r="D36" t="s">
         <v>195</v>
       </c>
       <c r="E36" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F36" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B37" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="D37" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>227</v>
+        <v>383</v>
       </c>
       <c r="F37" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="D38" t="s">
         <v>195</v>
       </c>
       <c r="E38" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F38" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C39" t="s">
-        <v>294</v>
+        <v>392</v>
       </c>
       <c r="D39" t="s">
         <v>195</v>
       </c>
       <c r="E39" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F39" t="s">
-        <v>227</v>
+        <v>394</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B40" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C40" t="s">
-        <v>294</v>
+        <v>178</v>
       </c>
       <c r="D40" t="s">
-        <v>195</v>
+        <v>398</v>
       </c>
       <c r="E40" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F40" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C41" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D41" t="s">
         <v>195</v>
       </c>
       <c r="E41" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F41" t="s">
-        <v>284</v>
+        <v>405</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C42" t="s">
-        <v>178</v>
+        <v>409</v>
       </c>
       <c r="D42" t="s">
-        <v>335</v>
+        <v>195</v>
       </c>
       <c r="E42" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="F42" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C43" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D43" t="s">
         <v>195</v>
       </c>
       <c r="E43" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F43" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C44" t="s">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="D44" t="s">
-        <v>352</v>
+        <v>420</v>
       </c>
       <c r="E44" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="F44" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C45" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D45" t="s">
-        <v>352</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="F45" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>419</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>431</v>
       </c>
       <c r="D46" t="s">
-        <v>421</v>
+        <v>195</v>
       </c>
       <c r="E46" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F46" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C47" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="D47" t="s">
         <v>195</v>
       </c>
       <c r="E47" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F47" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B48" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C48" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D48" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E48" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="F48" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s">
-        <v>436</v>
+        <v>296</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>297</v>
       </c>
       <c r="D49" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="E49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F49" t="s">
-        <v>438</v>
+        <v>299</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="C50" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="D50" t="s">
         <v>195</v>
       </c>
       <c r="E50" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="F50" t="s">
-        <v>227</v>
+        <v>452</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="C51" t="s">
-        <v>446</v>
+        <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E51" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="F51" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="C52" t="s">
-        <v>178</v>
+        <v>263</v>
       </c>
       <c r="D52" t="s">
         <v>195</v>
       </c>
       <c r="E52" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="F52" t="s">
-        <v>452</v>
+        <v>264</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C53" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D53" t="s">
-        <v>195</v>
+        <v>420</v>
       </c>
       <c r="E53" t="s">
-        <v>227</v>
+        <v>464</v>
       </c>
       <c r="F53" t="s">
-        <v>227</v>
+        <v>465</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B54" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C54" t="s">
         <v>178</v>
       </c>
       <c r="D54" t="s">
-        <v>335</v>
+        <v>195</v>
       </c>
       <c r="E54" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F54" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C55" t="s">
-        <v>432</v>
+        <v>342</v>
       </c>
       <c r="D55" t="s">
         <v>195</v>
       </c>
       <c r="E55" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F55" t="s">
-        <v>466</v>
+        <v>264</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="D56" t="s">
         <v>195</v>
       </c>
       <c r="E56" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="F56" t="s">
-        <v>296</v>
+        <v>479</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="D57" t="s">
         <v>195</v>
       </c>
       <c r="E57" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="F57" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B58" t="s">
-        <v>475</v>
+        <v>200</v>
       </c>
       <c r="C58" t="s">
-        <v>294</v>
+        <v>201</v>
       </c>
       <c r="D58" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="E58" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="F58" t="s">
-        <v>477</v>
+        <v>203</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B59" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C59" t="s">
-        <v>481</v>
+        <v>178</v>
       </c>
       <c r="D59" t="s">
-        <v>195</v>
+        <v>398</v>
       </c>
       <c r="E59" t="s">
-        <v>482</v>
+        <v>264</v>
       </c>
       <c r="F59" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B60" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C60" t="s">
-        <v>294</v>
+        <v>494</v>
       </c>
       <c r="D60" t="s">
         <v>195</v>
       </c>
       <c r="E60" t="s">
-        <v>310</v>
+        <v>495</v>
       </c>
       <c r="F60" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="C61" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D61" t="s">
-        <v>195</v>
+        <v>420</v>
       </c>
       <c r="E61" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="F61" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C62" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D62" t="s">
-        <v>352</v>
+        <v>420</v>
       </c>
       <c r="E62" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F62" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s">
-        <v>384</v>
+        <v>507</v>
       </c>
       <c r="C63" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="D63" t="s">
         <v>195</v>
       </c>
       <c r="E63" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="F63" t="s">
-        <v>503</v>
+        <v>457</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B64" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C64" t="s">
-        <v>507</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s">
-        <v>195</v>
+        <v>512</v>
       </c>
       <c r="E64" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="F64" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B65" t="s">
-        <v>259</v>
+        <v>517</v>
       </c>
       <c r="C65" t="s">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="D65" t="s">
         <v>195</v>
       </c>
       <c r="E65" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F65" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B66" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C66" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="D66" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="E66" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F66" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B67" t="s">
-        <v>521</v>
+        <v>462</v>
       </c>
       <c r="C67" t="s">
-        <v>522</v>
+        <v>463</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>526</v>
       </c>
       <c r="F67" t="s">
-        <v>523</v>
+        <v>465</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B68" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C68" t="s">
-        <v>527</v>
+        <v>178</v>
       </c>
       <c r="D68" t="s">
         <v>195</v>
       </c>
       <c r="E68" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F68" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B69" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C69" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="D69" t="s">
         <v>195</v>
       </c>
       <c r="E69" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F69" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B70" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C70" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="D70" t="s">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="E70" t="s">
-        <v>227</v>
+        <v>540</v>
       </c>
       <c r="F70" t="s">
-        <v>537</v>
+        <v>405</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C71" t="s">
-        <v>541</v>
+        <v>178</v>
       </c>
       <c r="D71" t="s">
         <v>195</v>
       </c>
       <c r="E71" t="s">
-        <v>542</v>
+        <v>264</v>
       </c>
       <c r="F71" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B72" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C72" t="s">
-        <v>546</v>
+        <v>178</v>
       </c>
       <c r="D72" t="s">
-        <v>195</v>
+        <v>398</v>
       </c>
       <c r="E72" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F72" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B73" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C73" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
       <c r="D73" t="s">
         <v>195</v>
       </c>
       <c r="E73" t="s">
-        <v>552</v>
+        <v>264</v>
       </c>
       <c r="F73" t="s">
-        <v>553</v>
+        <v>264</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>554</v>
@@ -4881,252 +5304,1011 @@
         <v>555</v>
       </c>
       <c r="B74" t="s">
-        <v>225</v>
+        <v>556</v>
       </c>
       <c r="C74" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="D74" t="s">
-        <v>195</v>
+        <v>398</v>
       </c>
       <c r="E74" t="s">
-        <v>227</v>
+        <v>557</v>
       </c>
       <c r="F74" t="s">
-        <v>227</v>
+        <v>558</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C75" t="s">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="D75" t="s">
         <v>195</v>
       </c>
       <c r="E75" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F75" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B76" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C76" t="s">
-        <v>288</v>
+        <v>567</v>
       </c>
       <c r="D76" t="s">
         <v>195</v>
       </c>
       <c r="E76" t="s">
-        <v>559</v>
+        <v>264</v>
       </c>
       <c r="F76" t="s">
-        <v>560</v>
+        <v>264</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B77" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C77" t="s">
-        <v>565</v>
+        <v>178</v>
       </c>
       <c r="D77" t="s">
         <v>195</v>
       </c>
       <c r="E77" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F77" t="s">
-        <v>567</v>
+        <v>344</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B78" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C78" t="s">
-        <v>565</v>
+        <v>178</v>
       </c>
       <c r="D78" t="s">
         <v>195</v>
       </c>
       <c r="E78" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F78" t="s">
-        <v>567</v>
+        <v>344</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B79" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C79" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
       <c r="D79" t="s">
         <v>195</v>
       </c>
       <c r="E79" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F79" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>581</v>
       </c>
       <c r="C80" t="s">
-        <v>226</v>
+        <v>582</v>
       </c>
       <c r="D80" t="s">
         <v>195</v>
       </c>
       <c r="E80" t="s">
-        <v>227</v>
+        <v>583</v>
       </c>
       <c r="F80" t="s">
-        <v>227</v>
+        <v>584</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B81" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="D81" t="s">
         <v>195</v>
       </c>
       <c r="E81" t="s">
-        <v>580</v>
+        <v>358</v>
       </c>
       <c r="F81" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B82" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C82" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="D82" t="s">
         <v>195</v>
       </c>
       <c r="E82" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="F82" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B83" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C83" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E83" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F83" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B84" t="s">
-        <v>259</v>
+        <v>462</v>
       </c>
       <c r="C84" t="s">
-        <v>260</v>
+        <v>463</v>
       </c>
       <c r="D84" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="E84" t="s">
-        <v>596</v>
+        <v>264</v>
       </c>
       <c r="F84" t="s">
+        <v>603</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>605</v>
+      </c>
+      <c r="B85" t="s">
+        <v>462</v>
+      </c>
+      <c r="C85" t="s">
+        <v>463</v>
+      </c>
+      <c r="D85" t="s">
+        <v>195</v>
+      </c>
+      <c r="E85" t="s">
+        <v>264</v>
+      </c>
+      <c r="F85" t="s">
+        <v>465</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>607</v>
+      </c>
+      <c r="B86" t="s">
+        <v>608</v>
+      </c>
+      <c r="C86" t="s">
+        <v>609</v>
+      </c>
+      <c r="D86" t="s">
+        <v>420</v>
+      </c>
+      <c r="E86" t="s">
+        <v>610</v>
+      </c>
+      <c r="F86" t="s">
+        <v>611</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>613</v>
+      </c>
+      <c r="B87" t="s">
+        <v>538</v>
+      </c>
+      <c r="C87" t="s">
+        <v>539</v>
+      </c>
+      <c r="D87" t="s">
+        <v>195</v>
+      </c>
+      <c r="E87" t="s">
+        <v>614</v>
+      </c>
+      <c r="F87" t="s">
+        <v>615</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>617</v>
+      </c>
+      <c r="B88" t="s">
+        <v>468</v>
+      </c>
+      <c r="C88" t="s">
+        <v>178</v>
+      </c>
+      <c r="D88" t="s">
+        <v>195</v>
+      </c>
+      <c r="E88" t="s">
+        <v>618</v>
+      </c>
+      <c r="F88" t="s">
+        <v>619</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>621</v>
+      </c>
+      <c r="B89" t="s">
+        <v>622</v>
+      </c>
+      <c r="C89" t="s">
+        <v>201</v>
+      </c>
+      <c r="D89" t="s">
+        <v>195</v>
+      </c>
+      <c r="E89" t="s">
+        <v>623</v>
+      </c>
+      <c r="F89" t="s">
+        <v>624</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>626</v>
+      </c>
+      <c r="B90" t="s">
+        <v>627</v>
+      </c>
+      <c r="C90" t="s">
+        <v>628</v>
+      </c>
+      <c r="D90" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" t="s">
+        <v>202</v>
+      </c>
+      <c r="F90" t="s">
+        <v>629</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>631</v>
+      </c>
+      <c r="B91" t="s">
+        <v>413</v>
+      </c>
+      <c r="C91" t="s">
+        <v>414</v>
+      </c>
+      <c r="D91" t="s">
+        <v>195</v>
+      </c>
+      <c r="E91" t="s">
+        <v>415</v>
+      </c>
+      <c r="F91" t="s">
+        <v>416</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>633</v>
+      </c>
+      <c r="B92" t="s">
+        <v>296</v>
+      </c>
+      <c r="C92" t="s">
+        <v>297</v>
+      </c>
+      <c r="D92" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" t="s">
+        <v>634</v>
+      </c>
+      <c r="F92" t="s">
+        <v>635</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>637</v>
+      </c>
+      <c r="B93" t="s">
+        <v>638</v>
+      </c>
+      <c r="C93" t="s">
+        <v>178</v>
+      </c>
+      <c r="D93" t="s">
+        <v>195</v>
+      </c>
+      <c r="E93" t="s">
+        <v>639</v>
+      </c>
+      <c r="F93" t="s">
+        <v>640</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>642</v>
+      </c>
+      <c r="B94" t="s">
+        <v>643</v>
+      </c>
+      <c r="C94" t="s">
+        <v>178</v>
+      </c>
+      <c r="D94" t="s">
+        <v>420</v>
+      </c>
+      <c r="E94" t="s">
+        <v>644</v>
+      </c>
+      <c r="F94" t="s">
+        <v>645</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>647</v>
+      </c>
+      <c r="B95" t="s">
+        <v>462</v>
+      </c>
+      <c r="C95" t="s">
+        <v>463</v>
+      </c>
+      <c r="D95" t="s">
+        <v>195</v>
+      </c>
+      <c r="E95" t="s">
+        <v>264</v>
+      </c>
+      <c r="F95" t="s">
+        <v>648</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>650</v>
+      </c>
+      <c r="B96" t="s">
+        <v>367</v>
+      </c>
+      <c r="C96" t="s">
+        <v>368</v>
+      </c>
+      <c r="D96" t="s">
+        <v>195</v>
+      </c>
+      <c r="E96" t="s">
+        <v>309</v>
+      </c>
+      <c r="F96" t="s">
+        <v>370</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>652</v>
+      </c>
+      <c r="B97" t="s">
+        <v>653</v>
+      </c>
+      <c r="C97" t="s">
+        <v>654</v>
+      </c>
+      <c r="D97" t="s">
+        <v>195</v>
+      </c>
+      <c r="E97" t="s">
+        <v>245</v>
+      </c>
+      <c r="F97" t="s">
+        <v>655</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>657</v>
+      </c>
+      <c r="B98" t="s">
+        <v>658</v>
+      </c>
+      <c r="C98" t="s">
+        <v>178</v>
+      </c>
+      <c r="D98" t="s">
+        <v>195</v>
+      </c>
+      <c r="E98" t="s">
+        <v>659</v>
+      </c>
+      <c r="F98" t="s">
+        <v>322</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>661</v>
+      </c>
+      <c r="B99" t="s">
+        <v>662</v>
+      </c>
+      <c r="C99" t="s">
+        <v>368</v>
+      </c>
+      <c r="D99" t="s">
+        <v>195</v>
+      </c>
+      <c r="E99" t="s">
+        <v>264</v>
+      </c>
+      <c r="F99" t="s">
+        <v>663</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>665</v>
+      </c>
+      <c r="B100" t="s">
+        <v>666</v>
+      </c>
+      <c r="C100" t="s">
+        <v>667</v>
+      </c>
+      <c r="D100" t="s">
+        <v>195</v>
+      </c>
+      <c r="E100" t="s">
+        <v>668</v>
+      </c>
+      <c r="F100" t="s">
+        <v>588</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>670</v>
+      </c>
+      <c r="B101" t="s">
+        <v>671</v>
+      </c>
+      <c r="C101" t="s">
+        <v>672</v>
+      </c>
+      <c r="D101" t="s">
+        <v>195</v>
+      </c>
+      <c r="E101" t="s">
+        <v>599</v>
+      </c>
+      <c r="F101" t="s">
+        <v>673</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>675</v>
+      </c>
+      <c r="B102" t="s">
+        <v>676</v>
+      </c>
+      <c r="C102" t="s">
+        <v>178</v>
+      </c>
+      <c r="D102" t="s">
+        <v>195</v>
+      </c>
+      <c r="E102" t="s">
+        <v>677</v>
+      </c>
+      <c r="F102" t="s">
+        <v>678</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>680</v>
+      </c>
+      <c r="B103" t="s">
         <v>262</v>
       </c>
-      <c r="H84" s="2" t="s">
-        <v>597</v>
+      <c r="C103" t="s">
+        <v>263</v>
+      </c>
+      <c r="D103" t="s">
+        <v>195</v>
+      </c>
+      <c r="E103" t="s">
+        <v>264</v>
+      </c>
+      <c r="F103" t="s">
+        <v>264</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>682</v>
+      </c>
+      <c r="B104" t="s">
+        <v>683</v>
+      </c>
+      <c r="C104" t="s">
+        <v>426</v>
+      </c>
+      <c r="D104" t="s">
+        <v>195</v>
+      </c>
+      <c r="E104" t="s">
+        <v>684</v>
+      </c>
+      <c r="F104" t="s">
+        <v>685</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>682</v>
+      </c>
+      <c r="B105" t="s">
+        <v>683</v>
+      </c>
+      <c r="C105" t="s">
+        <v>207</v>
+      </c>
+      <c r="D105" t="s">
+        <v>195</v>
+      </c>
+      <c r="E105" t="s">
+        <v>684</v>
+      </c>
+      <c r="F105" t="s">
+        <v>685</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>688</v>
+      </c>
+      <c r="B106" t="s">
+        <v>689</v>
+      </c>
+      <c r="C106" t="s">
+        <v>690</v>
+      </c>
+      <c r="D106" t="s">
+        <v>195</v>
+      </c>
+      <c r="E106" t="s">
+        <v>691</v>
+      </c>
+      <c r="F106" t="s">
+        <v>692</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>694</v>
+      </c>
+      <c r="B107" t="s">
+        <v>695</v>
+      </c>
+      <c r="C107" t="s">
+        <v>215</v>
+      </c>
+      <c r="D107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E107" t="s">
+        <v>696</v>
+      </c>
+      <c r="F107" t="s">
+        <v>697</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>699</v>
+      </c>
+      <c r="B108" t="s">
+        <v>695</v>
+      </c>
+      <c r="C108" t="s">
+        <v>215</v>
+      </c>
+      <c r="D108" t="s">
+        <v>195</v>
+      </c>
+      <c r="E108" t="s">
+        <v>696</v>
+      </c>
+      <c r="F108" t="s">
+        <v>697</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>701</v>
+      </c>
+      <c r="B109" t="s">
+        <v>702</v>
+      </c>
+      <c r="C109" t="s">
+        <v>325</v>
+      </c>
+      <c r="D109" t="s">
+        <v>195</v>
+      </c>
+      <c r="E109" t="s">
+        <v>703</v>
+      </c>
+      <c r="F109" t="s">
+        <v>704</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>706</v>
+      </c>
+      <c r="B110" t="s">
+        <v>507</v>
+      </c>
+      <c r="C110" t="s">
+        <v>211</v>
+      </c>
+      <c r="D110" t="s">
+        <v>195</v>
+      </c>
+      <c r="E110" t="s">
+        <v>707</v>
+      </c>
+      <c r="F110" t="s">
+        <v>457</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>709</v>
+      </c>
+      <c r="B111" t="s">
+        <v>710</v>
+      </c>
+      <c r="C111" t="s">
+        <v>178</v>
+      </c>
+      <c r="D111" t="s">
+        <v>195</v>
+      </c>
+      <c r="E111" t="s">
+        <v>711</v>
+      </c>
+      <c r="F111" t="s">
+        <v>712</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>714</v>
+      </c>
+      <c r="B112" t="s">
+        <v>262</v>
+      </c>
+      <c r="C112" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" t="s">
+        <v>195</v>
+      </c>
+      <c r="E112" t="s">
+        <v>264</v>
+      </c>
+      <c r="F112" t="s">
+        <v>264</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>716</v>
+      </c>
+      <c r="B113" t="s">
+        <v>717</v>
+      </c>
+      <c r="C113" t="s">
+        <v>178</v>
+      </c>
+      <c r="D113" t="s">
+        <v>195</v>
+      </c>
+      <c r="E113" t="s">
+        <v>718</v>
+      </c>
+      <c r="F113" t="s">
+        <v>719</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>721</v>
+      </c>
+      <c r="B114" t="s">
+        <v>722</v>
+      </c>
+      <c r="C114" t="s">
+        <v>211</v>
+      </c>
+      <c r="D114" t="s">
+        <v>195</v>
+      </c>
+      <c r="E114" t="s">
+        <v>723</v>
+      </c>
+      <c r="F114" t="s">
+        <v>692</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>725</v>
+      </c>
+      <c r="B115" t="s">
+        <v>726</v>
+      </c>
+      <c r="C115" t="s">
+        <v>727</v>
+      </c>
+      <c r="D115" t="s">
+        <v>420</v>
+      </c>
+      <c r="E115" t="s">
+        <v>728</v>
+      </c>
+      <c r="F115" t="s">
+        <v>729</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>731</v>
+      </c>
+      <c r="B116" t="s">
+        <v>732</v>
+      </c>
+      <c r="C116" t="s">
+        <v>733</v>
+      </c>
+      <c r="D116" t="s">
+        <v>251</v>
+      </c>
+      <c r="E116" t="s">
+        <v>734</v>
+      </c>
+      <c r="F116" t="s">
+        <v>735</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>737</v>
+      </c>
+      <c r="B117" t="s">
+        <v>296</v>
+      </c>
+      <c r="C117" t="s">
+        <v>297</v>
+      </c>
+      <c r="D117" t="s">
+        <v>251</v>
+      </c>
+      <c r="E117" t="s">
+        <v>486</v>
+      </c>
+      <c r="F117" t="s">
+        <v>299</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -5215,6 +6397,39 @@
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
     <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-13.xlsx
+++ b/docs/xlsx/jobs-2026-10-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="740">
   <si>
     <t>Title</t>
   </si>
@@ -2039,6 +2039,9 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/85a8a20f0f014a60bc7e1956d6216bf9-social-media-manager-chesapeake-climate-action-network-takoma-park</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85a8a20f0f014a60bc7e1956d6216bf9-social-media-manager-chesapeake-climate-action-network-washington</t>
   </si>
   <si>
     <t>Software Engineer (Early Career)</t>
@@ -3604,7 +3607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5945,91 +5948,91 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>670</v>
+      </c>
+      <c r="B102" t="s">
+        <v>671</v>
+      </c>
+      <c r="C102" t="s">
+        <v>201</v>
+      </c>
+      <c r="D102" t="s">
+        <v>195</v>
+      </c>
+      <c r="E102" t="s">
+        <v>599</v>
+      </c>
+      <c r="F102" t="s">
+        <v>673</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="B102" t="s">
-        <v>676</v>
-      </c>
-      <c r="C102" t="s">
-        <v>178</v>
-      </c>
-      <c r="D102" t="s">
-        <v>195</v>
-      </c>
-      <c r="E102" t="s">
-        <v>677</v>
-      </c>
-      <c r="F102" t="s">
-        <v>678</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>676</v>
+      </c>
+      <c r="B103" t="s">
+        <v>677</v>
+      </c>
+      <c r="C103" t="s">
+        <v>178</v>
+      </c>
+      <c r="D103" t="s">
+        <v>195</v>
+      </c>
+      <c r="E103" t="s">
+        <v>678</v>
+      </c>
+      <c r="F103" t="s">
+        <v>679</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B103" t="s">
-        <v>262</v>
-      </c>
-      <c r="C103" t="s">
-        <v>263</v>
-      </c>
-      <c r="D103" t="s">
-        <v>195</v>
-      </c>
-      <c r="E103" t="s">
-        <v>264</v>
-      </c>
-      <c r="F103" t="s">
-        <v>264</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>681</v>
+      </c>
+      <c r="B104" t="s">
+        <v>262</v>
+      </c>
+      <c r="C104" t="s">
+        <v>263</v>
+      </c>
+      <c r="D104" t="s">
+        <v>195</v>
+      </c>
+      <c r="E104" t="s">
+        <v>264</v>
+      </c>
+      <c r="F104" t="s">
+        <v>264</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="B104" t="s">
-        <v>683</v>
-      </c>
-      <c r="C104" t="s">
-        <v>426</v>
-      </c>
-      <c r="D104" t="s">
-        <v>195</v>
-      </c>
-      <c r="E104" t="s">
-        <v>684</v>
-      </c>
-      <c r="F104" t="s">
-        <v>685</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B105" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C105" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="D105" t="s">
         <v>195</v>
       </c>
       <c r="E105" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F105" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>687</v>
@@ -6037,56 +6040,56 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>683</v>
+      </c>
+      <c r="B106" t="s">
+        <v>684</v>
+      </c>
+      <c r="C106" t="s">
+        <v>207</v>
+      </c>
+      <c r="D106" t="s">
+        <v>195</v>
+      </c>
+      <c r="E106" t="s">
+        <v>685</v>
+      </c>
+      <c r="F106" t="s">
+        <v>686</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="B106" t="s">
-        <v>689</v>
-      </c>
-      <c r="C106" t="s">
-        <v>690</v>
-      </c>
-      <c r="D106" t="s">
-        <v>195</v>
-      </c>
-      <c r="E106" t="s">
-        <v>691</v>
-      </c>
-      <c r="F106" t="s">
-        <v>692</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>689</v>
+      </c>
+      <c r="B107" t="s">
+        <v>690</v>
+      </c>
+      <c r="C107" t="s">
+        <v>691</v>
+      </c>
+      <c r="D107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E107" t="s">
+        <v>692</v>
+      </c>
+      <c r="F107" t="s">
+        <v>693</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="B107" t="s">
-        <v>695</v>
-      </c>
-      <c r="C107" t="s">
-        <v>215</v>
-      </c>
-      <c r="D107" t="s">
-        <v>195</v>
-      </c>
-      <c r="E107" t="s">
-        <v>696</v>
-      </c>
-      <c r="F107" t="s">
-        <v>697</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B108" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C108" t="s">
         <v>215</v>
@@ -6095,220 +6098,243 @@
         <v>195</v>
       </c>
       <c r="E108" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F108" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>700</v>
+      </c>
+      <c r="B109" t="s">
+        <v>696</v>
+      </c>
+      <c r="C109" t="s">
+        <v>215</v>
+      </c>
+      <c r="D109" t="s">
+        <v>195</v>
+      </c>
+      <c r="E109" t="s">
+        <v>697</v>
+      </c>
+      <c r="F109" t="s">
+        <v>698</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="B109" t="s">
-        <v>702</v>
-      </c>
-      <c r="C109" t="s">
-        <v>325</v>
-      </c>
-      <c r="D109" t="s">
-        <v>195</v>
-      </c>
-      <c r="E109" t="s">
-        <v>703</v>
-      </c>
-      <c r="F109" t="s">
-        <v>704</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>702</v>
+      </c>
+      <c r="B110" t="s">
+        <v>703</v>
+      </c>
+      <c r="C110" t="s">
+        <v>325</v>
+      </c>
+      <c r="D110" t="s">
+        <v>195</v>
+      </c>
+      <c r="E110" t="s">
+        <v>704</v>
+      </c>
+      <c r="F110" t="s">
+        <v>705</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="B110" t="s">
-        <v>507</v>
-      </c>
-      <c r="C110" t="s">
-        <v>211</v>
-      </c>
-      <c r="D110" t="s">
-        <v>195</v>
-      </c>
-      <c r="E110" t="s">
-        <v>707</v>
-      </c>
-      <c r="F110" t="s">
-        <v>457</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>707</v>
+      </c>
+      <c r="B111" t="s">
+        <v>507</v>
+      </c>
+      <c r="C111" t="s">
+        <v>211</v>
+      </c>
+      <c r="D111" t="s">
+        <v>195</v>
+      </c>
+      <c r="E111" t="s">
+        <v>708</v>
+      </c>
+      <c r="F111" t="s">
+        <v>457</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="B111" t="s">
-        <v>710</v>
-      </c>
-      <c r="C111" t="s">
-        <v>178</v>
-      </c>
-      <c r="D111" t="s">
-        <v>195</v>
-      </c>
-      <c r="E111" t="s">
-        <v>711</v>
-      </c>
-      <c r="F111" t="s">
-        <v>712</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>710</v>
+      </c>
+      <c r="B112" t="s">
+        <v>711</v>
+      </c>
+      <c r="C112" t="s">
+        <v>178</v>
+      </c>
+      <c r="D112" t="s">
+        <v>195</v>
+      </c>
+      <c r="E112" t="s">
+        <v>712</v>
+      </c>
+      <c r="F112" t="s">
+        <v>713</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="B112" t="s">
-        <v>262</v>
-      </c>
-      <c r="C112" t="s">
-        <v>263</v>
-      </c>
-      <c r="D112" t="s">
-        <v>195</v>
-      </c>
-      <c r="E112" t="s">
-        <v>264</v>
-      </c>
-      <c r="F112" t="s">
-        <v>264</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>715</v>
+      </c>
+      <c r="B113" t="s">
+        <v>262</v>
+      </c>
+      <c r="C113" t="s">
+        <v>263</v>
+      </c>
+      <c r="D113" t="s">
+        <v>195</v>
+      </c>
+      <c r="E113" t="s">
+        <v>264</v>
+      </c>
+      <c r="F113" t="s">
+        <v>264</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="B113" t="s">
-        <v>717</v>
-      </c>
-      <c r="C113" t="s">
-        <v>178</v>
-      </c>
-      <c r="D113" t="s">
-        <v>195</v>
-      </c>
-      <c r="E113" t="s">
-        <v>718</v>
-      </c>
-      <c r="F113" t="s">
-        <v>719</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>717</v>
+      </c>
+      <c r="B114" t="s">
+        <v>718</v>
+      </c>
+      <c r="C114" t="s">
+        <v>178</v>
+      </c>
+      <c r="D114" t="s">
+        <v>195</v>
+      </c>
+      <c r="E114" t="s">
+        <v>719</v>
+      </c>
+      <c r="F114" t="s">
+        <v>720</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="B114" t="s">
-        <v>722</v>
-      </c>
-      <c r="C114" t="s">
-        <v>211</v>
-      </c>
-      <c r="D114" t="s">
-        <v>195</v>
-      </c>
-      <c r="E114" t="s">
-        <v>723</v>
-      </c>
-      <c r="F114" t="s">
-        <v>692</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>722</v>
+      </c>
+      <c r="B115" t="s">
+        <v>723</v>
+      </c>
+      <c r="C115" t="s">
+        <v>211</v>
+      </c>
+      <c r="D115" t="s">
+        <v>195</v>
+      </c>
+      <c r="E115" t="s">
+        <v>724</v>
+      </c>
+      <c r="F115" t="s">
+        <v>693</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="B115" t="s">
-        <v>726</v>
-      </c>
-      <c r="C115" t="s">
-        <v>727</v>
-      </c>
-      <c r="D115" t="s">
-        <v>420</v>
-      </c>
-      <c r="E115" t="s">
-        <v>728</v>
-      </c>
-      <c r="F115" t="s">
-        <v>729</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>726</v>
+      </c>
+      <c r="B116" t="s">
+        <v>727</v>
+      </c>
+      <c r="C116" t="s">
+        <v>728</v>
+      </c>
+      <c r="D116" t="s">
+        <v>420</v>
+      </c>
+      <c r="E116" t="s">
+        <v>729</v>
+      </c>
+      <c r="F116" t="s">
+        <v>730</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="B116" t="s">
-        <v>732</v>
-      </c>
-      <c r="C116" t="s">
-        <v>733</v>
-      </c>
-      <c r="D116" t="s">
-        <v>251</v>
-      </c>
-      <c r="E116" t="s">
-        <v>734</v>
-      </c>
-      <c r="F116" t="s">
-        <v>735</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="B117" t="s">
-        <v>296</v>
+        <v>733</v>
       </c>
       <c r="C117" t="s">
-        <v>297</v>
+        <v>734</v>
       </c>
       <c r="D117" t="s">
         <v>251</v>
       </c>
       <c r="E117" t="s">
+        <v>735</v>
+      </c>
+      <c r="F117" t="s">
+        <v>736</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>738</v>
+      </c>
+      <c r="B118" t="s">
+        <v>296</v>
+      </c>
+      <c r="C118" t="s">
+        <v>297</v>
+      </c>
+      <c r="D118" t="s">
+        <v>251</v>
+      </c>
+      <c r="E118" t="s">
         <v>486</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F118" t="s">
         <v>299</v>
       </c>
-      <c r="H117" s="2" t="s">
-        <v>738</v>
+      <c r="H118" s="2" t="s">
+        <v>739</v>
       </c>
     </row>
   </sheetData>
@@ -6430,6 +6456,7 @@
     <hyperlink ref="H115" r:id="rId114"/>
     <hyperlink ref="H116" r:id="rId115"/>
     <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
